--- a/research/traditional_assets/database/data/jordan/jordan_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_shipbuilding_marine.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1242867528498858</v>
+        <v>0.124074179344186</v>
       </c>
       <c r="C2">
-        <v>51.63370155699077</v>
+        <v>51.23580959024517</v>
       </c>
       <c r="D2">
-        <v>40.43370155699078</v>
+        <v>40.54350959024517</v>
       </c>
       <c r="E2">
-        <v>-6.570000000000001</v>
+        <v>-6.062300000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5077</v>
       </c>
       <c r="G2">
         <v>11.2</v>
@@ -1585,28 +1585,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02553731</v>
       </c>
       <c r="N2">
-        <v>2.862499999999999</v>
+        <v>2.83696269</v>
       </c>
       <c r="O2">
-        <v>0.5724999999999999</v>
+        <v>0.5673925379999999</v>
       </c>
       <c r="P2">
-        <v>2.29</v>
+        <v>2.269570152</v>
       </c>
       <c r="Q2">
-        <v>3.44</v>
+        <v>3.419570151999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1242867528498858</v>
+        <v>0.1249209892365515</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8664072619289552</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>112.0908975925812</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.124074179344186</v>
+        <v>0.1238616058384862</v>
       </c>
       <c r="C3">
-        <v>51.23580959024517</v>
+        <v>50.83851567111422</v>
       </c>
       <c r="D3">
-        <v>40.54350959024517</v>
+        <v>40.65391567111422</v>
       </c>
       <c r="E3">
-        <v>-6.062300000000001</v>
+        <v>-5.554600000000001</v>
       </c>
       <c r="F3">
-        <v>0.5077</v>
+        <v>1.0154</v>
       </c>
       <c r="G3">
         <v>11.2</v>
@@ -1667,28 +1667,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M3">
-        <v>0.02553731</v>
+        <v>0.05107462</v>
       </c>
       <c r="N3">
-        <v>2.83696269</v>
+        <v>2.811425379999999</v>
       </c>
       <c r="O3">
-        <v>0.5673925379999999</v>
+        <v>0.5622850759999999</v>
       </c>
       <c r="P3">
-        <v>2.269570152</v>
+        <v>2.249140304</v>
       </c>
       <c r="Q3">
-        <v>3.419570151999999</v>
+        <v>3.399140303999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1249209892365515</v>
+        <v>0.1255681692229451</v>
       </c>
       <c r="T3">
-        <v>0.8664072619289552</v>
+        <v>0.8734941480434614</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>112.0908975925812</v>
+        <v>56.04544879629059</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1238616058384862</v>
+        <v>0.1236490323327865</v>
       </c>
       <c r="C4">
-        <v>50.83851567111422</v>
+        <v>50.44182469865986</v>
       </c>
       <c r="D4">
-        <v>40.65391567111422</v>
+        <v>40.76492469865986</v>
       </c>
       <c r="E4">
-        <v>-5.554600000000001</v>
+        <v>-5.046900000000001</v>
       </c>
       <c r="F4">
-        <v>1.0154</v>
+        <v>1.5231</v>
       </c>
       <c r="G4">
         <v>11.2</v>
@@ -1749,28 +1749,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M4">
-        <v>0.05107462</v>
+        <v>0.07661193000000001</v>
       </c>
       <c r="N4">
-        <v>2.811425379999999</v>
+        <v>2.785888069999999</v>
       </c>
       <c r="O4">
-        <v>0.5622850759999999</v>
+        <v>0.5571776139999999</v>
       </c>
       <c r="P4">
-        <v>2.249140304</v>
+        <v>2.228710456</v>
       </c>
       <c r="Q4">
-        <v>3.399140303999999</v>
+        <v>3.378710455999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1255681692229451</v>
+        <v>0.126228693126584</v>
       </c>
       <c r="T4">
-        <v>0.8734941480434614</v>
+        <v>0.8807271555211531</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.04544879629059</v>
+        <v>37.36363253086039</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1236490323327865</v>
+        <v>0.1234364588270867</v>
       </c>
       <c r="C5">
-        <v>50.44182469865986</v>
+        <v>50.04574162559983</v>
       </c>
       <c r="D5">
-        <v>40.76492469865986</v>
+        <v>40.87654162559983</v>
       </c>
       <c r="E5">
-        <v>-5.046900000000001</v>
+        <v>-4.539200000000001</v>
       </c>
       <c r="F5">
-        <v>1.5231</v>
+        <v>2.0308</v>
       </c>
       <c r="G5">
         <v>11.2</v>
@@ -1831,28 +1831,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M5">
-        <v>0.07661193000000001</v>
+        <v>0.10214924</v>
       </c>
       <c r="N5">
-        <v>2.785888069999999</v>
+        <v>2.760350759999999</v>
       </c>
       <c r="O5">
-        <v>0.5571776139999999</v>
+        <v>0.5520701519999999</v>
       </c>
       <c r="P5">
-        <v>2.228710456</v>
+        <v>2.208280607999999</v>
       </c>
       <c r="Q5">
-        <v>3.378710455999999</v>
+        <v>3.358280607999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.126228693126584</v>
+        <v>0.126902977944882</v>
       </c>
       <c r="T5">
-        <v>0.8807271555211531</v>
+        <v>0.8881108506546305</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.36363253086039</v>
+        <v>28.02272439814529</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1234364588270867</v>
+        <v>0.1232238853213869</v>
       </c>
       <c r="C6">
-        <v>50.04574162559983</v>
+        <v>49.65027145904422</v>
       </c>
       <c r="D6">
-        <v>40.87654162559983</v>
+        <v>40.98877145904422</v>
       </c>
       <c r="E6">
-        <v>-4.539200000000001</v>
+        <v>-4.031500000000001</v>
       </c>
       <c r="F6">
-        <v>2.0308</v>
+        <v>2.5385</v>
       </c>
       <c r="G6">
         <v>11.2</v>
@@ -1913,28 +1913,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M6">
-        <v>0.10214924</v>
+        <v>0.12768655</v>
       </c>
       <c r="N6">
-        <v>2.760350759999999</v>
+        <v>2.734813449999999</v>
       </c>
       <c r="O6">
-        <v>0.5520701519999999</v>
+        <v>0.5469626899999999</v>
       </c>
       <c r="P6">
-        <v>2.208280607999999</v>
+        <v>2.187850759999999</v>
       </c>
       <c r="Q6">
-        <v>3.358280607999999</v>
+        <v>3.337850759999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.126902977944882</v>
+        <v>0.1275914582330389</v>
       </c>
       <c r="T6">
-        <v>0.8881108506546305</v>
+        <v>0.8956499920014438</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.02272439814529</v>
+        <v>22.41817951851624</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1232238853213869</v>
+        <v>0.1230113118156872</v>
       </c>
       <c r="C7">
-        <v>49.65027145904422</v>
+        <v>49.25541926124417</v>
       </c>
       <c r="D7">
-        <v>40.98877145904422</v>
+        <v>41.10161926124417</v>
       </c>
       <c r="E7">
-        <v>-4.031500000000001</v>
+        <v>-3.523800000000001</v>
       </c>
       <c r="F7">
-        <v>2.5385</v>
+        <v>3.0462</v>
       </c>
       <c r="G7">
         <v>11.2</v>
@@ -1995,28 +1995,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M7">
-        <v>0.12768655</v>
+        <v>0.15322386</v>
       </c>
       <c r="N7">
-        <v>2.734813449999999</v>
+        <v>2.709276139999999</v>
       </c>
       <c r="O7">
-        <v>0.5469626899999999</v>
+        <v>0.5418552279999999</v>
       </c>
       <c r="P7">
-        <v>2.187850759999999</v>
+        <v>2.167420911999999</v>
       </c>
       <c r="Q7">
-        <v>3.337850759999999</v>
+        <v>3.317420911999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1275914582330389</v>
+        <v>0.1282945870379651</v>
       </c>
       <c r="T7">
-        <v>0.8956499920014438</v>
+        <v>0.9033495406109556</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.41817951851624</v>
+        <v>18.68181626543019</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1230113118156872</v>
+        <v>0.1227987383099874</v>
       </c>
       <c r="C8">
-        <v>49.25541926124417</v>
+        <v>48.86119015035311</v>
       </c>
       <c r="D8">
-        <v>41.10161926124417</v>
+        <v>41.21509015035311</v>
       </c>
       <c r="E8">
-        <v>-3.523800000000001</v>
+        <v>-3.016100000000001</v>
       </c>
       <c r="F8">
-        <v>3.0462</v>
+        <v>3.5539</v>
       </c>
       <c r="G8">
         <v>11.2</v>
@@ -2077,28 +2077,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M8">
-        <v>0.15322386</v>
+        <v>0.17876117</v>
       </c>
       <c r="N8">
-        <v>2.709276139999999</v>
+        <v>2.683738829999999</v>
       </c>
       <c r="O8">
-        <v>0.5418552279999999</v>
+        <v>0.5367477659999998</v>
       </c>
       <c r="P8">
-        <v>2.167420911999999</v>
+        <v>2.146991063999999</v>
       </c>
       <c r="Q8">
-        <v>3.317420911999999</v>
+        <v>3.296991063999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1282945870379651</v>
+        <v>0.1290128368924595</v>
       </c>
       <c r="T8">
-        <v>0.9033495406109556</v>
+        <v>0.9112146709109944</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.68181626543019</v>
+        <v>16.01298537036874</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1227987383099874</v>
+        <v>0.1225861648042876</v>
       </c>
       <c r="C9">
-        <v>48.86119015035311</v>
+        <v>48.46758930120043</v>
       </c>
       <c r="D9">
-        <v>41.21509015035311</v>
+        <v>41.32918930120043</v>
       </c>
       <c r="E9">
-        <v>-3.016100000000001</v>
+        <v>-2.508400000000001</v>
       </c>
       <c r="F9">
-        <v>3.553900000000001</v>
+        <v>4.0616</v>
       </c>
       <c r="G9">
         <v>11.2</v>
@@ -2159,28 +2159,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M9">
-        <v>0.17876117</v>
+        <v>0.20429848</v>
       </c>
       <c r="N9">
-        <v>2.683738829999999</v>
+        <v>2.65820152</v>
       </c>
       <c r="O9">
-        <v>0.5367477659999998</v>
+        <v>0.531640304</v>
       </c>
       <c r="P9">
-        <v>2.146991063999999</v>
+        <v>2.126561216</v>
       </c>
       <c r="Q9">
-        <v>3.296991063999999</v>
+        <v>3.276561216</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1290128368924595</v>
+        <v>0.1297467008742257</v>
       </c>
       <c r="T9">
-        <v>0.9112146709109944</v>
+        <v>0.9192507823045123</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.01298537036874</v>
+        <v>14.01136219907265</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1225861648042876</v>
+        <v>0.1224815912985878</v>
       </c>
       <c r="C10">
-        <v>48.46758930120043</v>
+        <v>48.01625143635914</v>
       </c>
       <c r="D10">
-        <v>41.32918930120043</v>
+        <v>41.38555143635914</v>
       </c>
       <c r="E10">
-        <v>-2.508400000000001</v>
+        <v>-2.000700000000001</v>
       </c>
       <c r="F10">
-        <v>4.0616</v>
+        <v>4.5693</v>
       </c>
       <c r="G10">
         <v>11.2</v>
@@ -2241,45 +2241,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M10">
-        <v>0.20429848</v>
+        <v>0.23668974</v>
       </c>
       <c r="N10">
-        <v>2.65820152</v>
+        <v>2.625810259999999</v>
       </c>
       <c r="O10">
-        <v>0.531640304</v>
+        <v>0.5251620519999999</v>
       </c>
       <c r="P10">
-        <v>2.126561216</v>
+        <v>2.100648208</v>
       </c>
       <c r="Q10">
-        <v>3.276561216</v>
+        <v>3.250648207999999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1297467008742257</v>
+        <v>0.1304966937347119</v>
       </c>
       <c r="T10">
-        <v>0.9192507823045123</v>
+        <v>0.9274635115308546</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.01136219907265</v>
+        <v>12.09389135329651</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1224815912985878</v>
+        <v>0.122281017792888</v>
       </c>
       <c r="C11">
-        <v>48.01625143635914</v>
+        <v>47.61708614701622</v>
       </c>
       <c r="D11">
-        <v>41.38555143635914</v>
+        <v>41.49408614701622</v>
       </c>
       <c r="E11">
-        <v>-2.000700000000001</v>
+        <v>-1.493000000000001</v>
       </c>
       <c r="F11">
-        <v>4.5693</v>
+        <v>5.077</v>
       </c>
       <c r="G11">
         <v>11.2</v>
@@ -2323,28 +2323,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M11">
-        <v>0.23668974</v>
+        <v>0.2629886</v>
       </c>
       <c r="N11">
-        <v>2.625810259999999</v>
+        <v>2.599511399999999</v>
       </c>
       <c r="O11">
-        <v>0.5251620519999999</v>
+        <v>0.5199022799999999</v>
       </c>
       <c r="P11">
-        <v>2.100648208</v>
+        <v>2.07960912</v>
       </c>
       <c r="Q11">
-        <v>3.250648207999999</v>
+        <v>3.22960912</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1304966937347119</v>
+        <v>0.1312633531032089</v>
       </c>
       <c r="T11">
-        <v>0.9274635115308546</v>
+        <v>0.9358587458511158</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.09389135329651</v>
+        <v>10.88450221796686</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1222810177928881</v>
+        <v>0.1220804442871883</v>
       </c>
       <c r="C12">
-        <v>47.6170861470162</v>
+        <v>47.21849162486295</v>
       </c>
       <c r="D12">
-        <v>41.4940861470162</v>
+        <v>41.60319162486295</v>
       </c>
       <c r="E12">
-        <v>-1.493</v>
+        <v>-0.9853000000000005</v>
       </c>
       <c r="F12">
-        <v>5.077000000000001</v>
+        <v>5.584700000000001</v>
       </c>
       <c r="G12">
         <v>11.2</v>
@@ -2405,28 +2405,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M12">
-        <v>0.2629886</v>
+        <v>0.2892874600000001</v>
       </c>
       <c r="N12">
-        <v>2.599511399999999</v>
+        <v>2.573212539999999</v>
       </c>
       <c r="O12">
-        <v>0.5199022799999999</v>
+        <v>0.5146425079999999</v>
       </c>
       <c r="P12">
-        <v>2.07960912</v>
+        <v>2.058570032</v>
       </c>
       <c r="Q12">
-        <v>3.22960912</v>
+        <v>3.208570031999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.131263353103209</v>
+        <v>0.1320472407721217</v>
       </c>
       <c r="T12">
-        <v>0.9358587458511159</v>
+        <v>0.9444426371223941</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.88450221796686</v>
+        <v>9.895002016333507</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1220804442871883</v>
+        <v>0.1220430707814885</v>
       </c>
       <c r="C13">
-        <v>47.21849162486295</v>
+        <v>46.73118504689307</v>
       </c>
       <c r="D13">
-        <v>41.60319162486295</v>
+        <v>41.62358504689308</v>
       </c>
       <c r="E13">
-        <v>-0.9853000000000005</v>
+        <v>-0.4776000000000007</v>
       </c>
       <c r="F13">
-        <v>5.584700000000001</v>
+        <v>6.0924</v>
       </c>
       <c r="G13">
         <v>11.2</v>
@@ -2487,45 +2487,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M13">
-        <v>0.2892874600000001</v>
+        <v>0.3259434</v>
       </c>
       <c r="N13">
-        <v>2.573212539999999</v>
+        <v>2.536556599999999</v>
       </c>
       <c r="O13">
-        <v>0.5146425079999999</v>
+        <v>0.5073113199999999</v>
       </c>
       <c r="P13">
-        <v>2.058570032</v>
+        <v>2.02924528</v>
       </c>
       <c r="Q13">
-        <v>3.208570031999999</v>
+        <v>3.17924528</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1320472407721217</v>
+        <v>0.1328489440698733</v>
       </c>
       <c r="T13">
-        <v>0.9444426371223941</v>
+        <v>0.9532216168316561</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.895002016333507</v>
+        <v>8.782199608889149</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1220430707814885</v>
+        <v>0.1218560972757887</v>
       </c>
       <c r="C14">
-        <v>46.73118504689307</v>
+        <v>46.32581093389975</v>
       </c>
       <c r="D14">
-        <v>41.62358504689308</v>
+        <v>41.72591093389975</v>
       </c>
       <c r="E14">
-        <v>-0.4776000000000007</v>
+        <v>0.03009999999999913</v>
       </c>
       <c r="F14">
-        <v>6.0924</v>
+        <v>6.6001</v>
       </c>
       <c r="G14">
         <v>11.2</v>
@@ -2569,28 +2569,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M14">
-        <v>0.3259434</v>
+        <v>0.35310535</v>
       </c>
       <c r="N14">
-        <v>2.536556599999999</v>
+        <v>2.50939465</v>
       </c>
       <c r="O14">
-        <v>0.5073113199999999</v>
+        <v>0.5018789299999999</v>
       </c>
       <c r="P14">
-        <v>2.02924528</v>
+        <v>2.00751572</v>
       </c>
       <c r="Q14">
-        <v>3.17924528</v>
+        <v>3.15751572</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1328489440698733</v>
+        <v>0.1336690773284928</v>
       </c>
       <c r="T14">
-        <v>0.9532216168316561</v>
+        <v>0.9622024121664182</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.782199608889149</v>
+        <v>8.106645792820753</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1218560972757887</v>
+        <v>0.121758723770089</v>
       </c>
       <c r="C15">
-        <v>46.32581093389975</v>
+        <v>45.87160048749531</v>
       </c>
       <c r="D15">
-        <v>41.72591093389975</v>
+        <v>41.77940048749531</v>
       </c>
       <c r="E15">
-        <v>0.03009999999999913</v>
+        <v>0.5377999999999998</v>
       </c>
       <c r="F15">
-        <v>6.6001</v>
+        <v>7.107800000000001</v>
       </c>
       <c r="G15">
         <v>11.2</v>
@@ -2651,45 +2651,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M15">
-        <v>0.35310535</v>
+        <v>0.38595354</v>
       </c>
       <c r="N15">
-        <v>2.50939465</v>
+        <v>2.476546459999999</v>
       </c>
       <c r="O15">
-        <v>0.5018789299999999</v>
+        <v>0.4953092919999999</v>
       </c>
       <c r="P15">
-        <v>2.00751572</v>
+        <v>1.981237167999999</v>
       </c>
       <c r="Q15">
-        <v>3.15751572</v>
+        <v>3.131237167999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1336690773284928</v>
+        <v>0.1345082834535918</v>
       </c>
       <c r="T15">
-        <v>0.9622024121664182</v>
+        <v>0.9713920632066401</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.106645792820753</v>
+        <v>7.41669580229786</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.121758723770089</v>
+        <v>0.1215781502643892</v>
       </c>
       <c r="C16">
-        <v>45.87160048749531</v>
+        <v>45.46345758655011</v>
       </c>
       <c r="D16">
-        <v>41.77940048749531</v>
+        <v>41.87895758655011</v>
       </c>
       <c r="E16">
-        <v>0.5377999999999998</v>
+        <v>1.045500000000001</v>
       </c>
       <c r="F16">
-        <v>7.107800000000001</v>
+        <v>7.615500000000002</v>
       </c>
       <c r="G16">
         <v>11.2</v>
@@ -2733,28 +2733,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M16">
-        <v>0.38595354</v>
+        <v>0.4135216500000001</v>
       </c>
       <c r="N16">
-        <v>2.476546459999999</v>
+        <v>2.448978349999999</v>
       </c>
       <c r="O16">
-        <v>0.4953092919999999</v>
+        <v>0.4897956699999998</v>
       </c>
       <c r="P16">
-        <v>1.981237167999999</v>
+        <v>1.959182679999999</v>
       </c>
       <c r="Q16">
-        <v>3.131237167999999</v>
+        <v>3.109182679999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1345082834535918</v>
+        <v>0.1353672356051638</v>
       </c>
       <c r="T16">
-        <v>0.9713920632066401</v>
+        <v>0.980797941330161</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.41669580229786</v>
+        <v>6.922249415478001</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1215781502643892</v>
+        <v>0.1213975767586894</v>
       </c>
       <c r="C17">
-        <v>45.46345758655012</v>
+        <v>45.05579029276497</v>
       </c>
       <c r="D17">
-        <v>41.87895758655011</v>
+        <v>41.97899029276496</v>
       </c>
       <c r="E17">
-        <v>1.045499999999999</v>
+        <v>1.553199999999999</v>
       </c>
       <c r="F17">
-        <v>7.6155</v>
+        <v>8.123200000000001</v>
       </c>
       <c r="G17">
         <v>11.2</v>
@@ -2815,28 +2815,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M17">
-        <v>0.41352165</v>
+        <v>0.4410897600000001</v>
       </c>
       <c r="N17">
-        <v>2.44897835</v>
+        <v>2.421410239999999</v>
       </c>
       <c r="O17">
-        <v>0.4897956699999999</v>
+        <v>0.4842820479999999</v>
       </c>
       <c r="P17">
-        <v>1.95918268</v>
+        <v>1.937128191999999</v>
       </c>
       <c r="Q17">
-        <v>3.10918268</v>
+        <v>3.087128191999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1353672356051638</v>
+        <v>0.1362466389984398</v>
       </c>
       <c r="T17">
-        <v>0.980797941330161</v>
+        <v>0.9904277689328135</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.922249415478003</v>
+        <v>6.489608827010627</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1213975767586894</v>
+        <v>0.1213530032529896</v>
       </c>
       <c r="C18">
-        <v>45.05579029276497</v>
+        <v>44.57285636006237</v>
       </c>
       <c r="D18">
-        <v>41.97899029276496</v>
+        <v>42.00375636006238</v>
       </c>
       <c r="E18">
-        <v>1.553199999999999</v>
+        <v>2.060899999999999</v>
       </c>
       <c r="F18">
-        <v>8.123200000000001</v>
+        <v>8.6309</v>
       </c>
       <c r="G18">
         <v>11.2</v>
@@ -2897,45 +2897,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M18">
-        <v>0.4410897600000001</v>
+        <v>0.47728877</v>
       </c>
       <c r="N18">
-        <v>2.421410239999999</v>
+        <v>2.385211229999999</v>
       </c>
       <c r="O18">
-        <v>0.4842820479999999</v>
+        <v>0.4770422459999999</v>
       </c>
       <c r="P18">
-        <v>1.937128191999999</v>
+        <v>1.908168984</v>
       </c>
       <c r="Q18">
-        <v>3.087128191999999</v>
+        <v>3.058168983999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1362466389984398</v>
+        <v>0.1371472328349273</v>
       </c>
       <c r="T18">
-        <v>0.9904277689328135</v>
+        <v>1.000289640574084</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.489608827010627</v>
+        <v>5.997417454427011</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1213530032529896</v>
+        <v>0.1211804297472899</v>
       </c>
       <c r="C19">
-        <v>44.57285636006237</v>
+        <v>44.16131839458401</v>
       </c>
       <c r="D19">
-        <v>42.00375636006238</v>
+        <v>42.09991839458401</v>
       </c>
       <c r="E19">
-        <v>2.060899999999999</v>
+        <v>2.568600000000001</v>
       </c>
       <c r="F19">
-        <v>8.6309</v>
+        <v>9.138600000000002</v>
       </c>
       <c r="G19">
         <v>11.2</v>
@@ -2979,28 +2979,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M19">
-        <v>0.47728877</v>
+        <v>0.5053645800000002</v>
       </c>
       <c r="N19">
-        <v>2.385211229999999</v>
+        <v>2.357135419999999</v>
       </c>
       <c r="O19">
-        <v>0.4770422459999999</v>
+        <v>0.4714270839999999</v>
       </c>
       <c r="P19">
-        <v>1.908168984</v>
+        <v>1.885708335999999</v>
       </c>
       <c r="Q19">
-        <v>3.058168983999999</v>
+        <v>3.035708335999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1371472328349273</v>
+        <v>0.1380697923747438</v>
       </c>
       <c r="T19">
-        <v>1.000289640574084</v>
+        <v>1.01039204567002</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.997417454427011</v>
+        <v>5.664227595847732</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1211804297472899</v>
+        <v>0.1210078562415901</v>
       </c>
       <c r="C20">
-        <v>44.161318394584</v>
+        <v>43.7502217399006</v>
       </c>
       <c r="D20">
-        <v>42.099918394584</v>
+        <v>42.19652173990059</v>
       </c>
       <c r="E20">
-        <v>2.568599999999999</v>
+        <v>3.076299999999999</v>
       </c>
       <c r="F20">
-        <v>9.1386</v>
+        <v>9.6463</v>
       </c>
       <c r="G20">
         <v>11.2</v>
@@ -3061,28 +3061,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M20">
-        <v>0.5053645800000001</v>
+        <v>0.53344039</v>
       </c>
       <c r="N20">
-        <v>2.357135419999999</v>
+        <v>2.329059609999999</v>
       </c>
       <c r="O20">
-        <v>0.4714270839999999</v>
+        <v>0.4658119219999999</v>
       </c>
       <c r="P20">
-        <v>1.885708335999999</v>
+        <v>1.863247688</v>
       </c>
       <c r="Q20">
-        <v>3.035708335999999</v>
+        <v>3.013247687999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1380697923747438</v>
+        <v>0.139015131162457</v>
       </c>
       <c r="T20">
-        <v>1.01039204567002</v>
+        <v>1.02074389286709</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.664227595847732</v>
+        <v>5.366110353961011</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1210078562415901</v>
+        <v>0.1208352827358903</v>
       </c>
       <c r="C21">
-        <v>43.7502217399006</v>
+        <v>43.33956944092177</v>
       </c>
       <c r="D21">
-        <v>42.19652173990059</v>
+        <v>42.29356944092177</v>
       </c>
       <c r="E21">
-        <v>3.076299999999999</v>
+        <v>3.584000000000001</v>
       </c>
       <c r="F21">
-        <v>9.6463</v>
+        <v>10.154</v>
       </c>
       <c r="G21">
         <v>11.2</v>
@@ -3143,28 +3143,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M21">
-        <v>0.53344039</v>
+        <v>0.5615162000000001</v>
       </c>
       <c r="N21">
-        <v>2.329059609999999</v>
+        <v>2.300983799999999</v>
       </c>
       <c r="O21">
-        <v>0.4658119219999999</v>
+        <v>0.4601967599999999</v>
       </c>
       <c r="P21">
-        <v>1.863247688</v>
+        <v>1.840787039999999</v>
       </c>
       <c r="Q21">
-        <v>3.013247687999999</v>
+        <v>2.990787039999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.139015131162457</v>
+        <v>0.1399841034198629</v>
       </c>
       <c r="T21">
-        <v>1.02074389286709</v>
+        <v>1.031354536244087</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.366110353961011</v>
+        <v>5.097804836262958</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1208352827358903</v>
+        <v>0.1206627092301906</v>
       </c>
       <c r="C22">
-        <v>43.33956944092177</v>
+        <v>42.92936457063359</v>
       </c>
       <c r="D22">
-        <v>42.29356944092177</v>
+        <v>42.39106457063359</v>
       </c>
       <c r="E22">
-        <v>3.584000000000001</v>
+        <v>4.0917</v>
       </c>
       <c r="F22">
-        <v>10.154</v>
+        <v>10.6617</v>
       </c>
       <c r="G22">
         <v>11.2</v>
@@ -3225,28 +3225,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M22">
-        <v>0.5615162000000001</v>
+        <v>0.5895920100000001</v>
       </c>
       <c r="N22">
-        <v>2.300983799999999</v>
+        <v>2.272907989999999</v>
       </c>
       <c r="O22">
-        <v>0.4601967599999999</v>
+        <v>0.4545815979999999</v>
       </c>
       <c r="P22">
-        <v>1.840787039999999</v>
+        <v>1.818326391999999</v>
       </c>
       <c r="Q22">
-        <v>2.990787039999999</v>
+        <v>2.968326391999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1399841034198629</v>
+        <v>0.1409776066204944</v>
       </c>
       <c r="T22">
-        <v>1.031354536244087</v>
+        <v>1.042233803504046</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.097804836262958</v>
+        <v>4.855052225012342</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1206627092301906</v>
+        <v>0.1204901357244908</v>
       </c>
       <c r="C23">
-        <v>42.9293645706336</v>
+        <v>42.51961023042306</v>
       </c>
       <c r="D23">
-        <v>42.39106457063359</v>
+        <v>42.48901023042306</v>
       </c>
       <c r="E23">
-        <v>4.091699999999999</v>
+        <v>4.5994</v>
       </c>
       <c r="F23">
-        <v>10.6617</v>
+        <v>11.1694</v>
       </c>
       <c r="G23">
         <v>11.2</v>
@@ -3307,28 +3307,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M23">
-        <v>0.5895920100000001</v>
+        <v>0.6176678200000001</v>
       </c>
       <c r="N23">
-        <v>2.272907989999999</v>
+        <v>2.24483218</v>
       </c>
       <c r="O23">
-        <v>0.4545815979999999</v>
+        <v>0.4489664359999999</v>
       </c>
       <c r="P23">
-        <v>1.818326391999999</v>
+        <v>1.795865744</v>
       </c>
       <c r="Q23">
-        <v>2.968326391999999</v>
+        <v>2.945865744</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1409776066204944</v>
+        <v>0.1419965842621677</v>
       </c>
       <c r="T23">
-        <v>1.042233803504046</v>
+        <v>1.053392026334772</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.855052225012342</v>
+        <v>4.634368032966327</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1204901357244908</v>
+        <v>0.120777562218791</v>
       </c>
       <c r="C24">
-        <v>42.51961023042306</v>
+        <v>41.84902860430163</v>
       </c>
       <c r="D24">
-        <v>42.48901023042306</v>
+        <v>42.32612860430164</v>
       </c>
       <c r="E24">
-        <v>4.5994</v>
+        <v>5.1071</v>
       </c>
       <c r="F24">
-        <v>11.1694</v>
+        <v>11.6771</v>
       </c>
       <c r="G24">
         <v>11.2</v>
@@ -3389,45 +3389,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M24">
-        <v>0.6176678200000001</v>
+        <v>0.6749363800000001</v>
       </c>
       <c r="N24">
-        <v>2.24483218</v>
+        <v>2.187563619999999</v>
       </c>
       <c r="O24">
-        <v>0.4489664359999999</v>
+        <v>0.4375127239999999</v>
       </c>
       <c r="P24">
-        <v>1.795865744</v>
+        <v>1.750050895999999</v>
       </c>
       <c r="Q24">
-        <v>2.945865744</v>
+        <v>2.900050895999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1419965842621677</v>
+        <v>0.1430420288555728</v>
       </c>
       <c r="T24">
-        <v>1.053392026334772</v>
+        <v>1.064840073135129</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.634368032966327</v>
+        <v>4.241140476084574</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.120777562218791</v>
+        <v>0.1206249887130913</v>
       </c>
       <c r="C25">
-        <v>41.84902860430163</v>
+        <v>41.42763460895228</v>
       </c>
       <c r="D25">
-        <v>42.32612860430164</v>
+        <v>42.41243460895229</v>
       </c>
       <c r="E25">
-        <v>5.1071</v>
+        <v>5.6148</v>
       </c>
       <c r="F25">
-        <v>11.6771</v>
+        <v>12.1848</v>
       </c>
       <c r="G25">
         <v>11.2</v>
@@ -3471,28 +3471,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M25">
-        <v>0.6749363800000001</v>
+        <v>0.7042814400000001</v>
       </c>
       <c r="N25">
-        <v>2.187563619999999</v>
+        <v>2.158218559999999</v>
       </c>
       <c r="O25">
-        <v>0.4375127239999999</v>
+        <v>0.4316437119999998</v>
       </c>
       <c r="P25">
-        <v>1.750050895999999</v>
+        <v>1.726574847999999</v>
       </c>
       <c r="Q25">
-        <v>2.900050895999999</v>
+        <v>2.876574847999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1430420288555728</v>
+        <v>0.1441149851488043</v>
       </c>
       <c r="T25">
-        <v>1.064840073135129</v>
+        <v>1.076589384324968</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.241140476084574</v>
+        <v>4.06442628958105</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1206249887130913</v>
+        <v>0.1211724152073915</v>
       </c>
       <c r="C26">
-        <v>41.4276346089523</v>
+        <v>40.61189498558569</v>
       </c>
       <c r="D26">
-        <v>42.4124346089523</v>
+        <v>42.10439498558569</v>
       </c>
       <c r="E26">
-        <v>5.6148</v>
+        <v>6.1225</v>
       </c>
       <c r="F26">
-        <v>12.1848</v>
+        <v>12.6925</v>
       </c>
       <c r="G26">
         <v>11.2</v>
@@ -3553,45 +3553,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M26">
-        <v>0.7042814400000001</v>
+        <v>0.7780502500000001</v>
       </c>
       <c r="N26">
-        <v>2.158218559999999</v>
+        <v>2.084449749999999</v>
       </c>
       <c r="O26">
-        <v>0.4316437119999998</v>
+        <v>0.4168899499999998</v>
       </c>
       <c r="P26">
-        <v>1.726574847999999</v>
+        <v>1.667559799999999</v>
       </c>
       <c r="Q26">
-        <v>2.876574847999999</v>
+        <v>2.817559799999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1441149851488043</v>
+        <v>0.1452165536098553</v>
       </c>
       <c r="T26">
-        <v>1.076589384324968</v>
+        <v>1.088652010479869</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.2</v>
       </c>
       <c r="W26">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.06442628958105</v>
+        <v>3.679068286399239</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1211724152073915</v>
+        <v>0.1210478417016917</v>
       </c>
       <c r="C27">
-        <v>40.61189498558569</v>
+        <v>40.1738992052697</v>
       </c>
       <c r="D27">
-        <v>42.10439498558569</v>
+        <v>42.1740992052697</v>
       </c>
       <c r="E27">
-        <v>6.1225</v>
+        <v>6.630199999999999</v>
       </c>
       <c r="F27">
-        <v>12.6925</v>
+        <v>13.2002</v>
       </c>
       <c r="G27">
         <v>11.2</v>
@@ -3635,28 +3635,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M27">
-        <v>0.7780502500000001</v>
+        <v>0.8091722600000001</v>
       </c>
       <c r="N27">
-        <v>2.084449749999999</v>
+        <v>2.053327739999999</v>
       </c>
       <c r="O27">
-        <v>0.4168899499999998</v>
+        <v>0.4106655479999999</v>
       </c>
       <c r="P27">
-        <v>1.667559799999999</v>
+        <v>1.642662192</v>
       </c>
       <c r="Q27">
-        <v>2.817559799999999</v>
+        <v>2.792662191999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1452165536098553</v>
+        <v>0.1463478941914753</v>
       </c>
       <c r="T27">
-        <v>1.088652010479869</v>
+        <v>1.101040653557877</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.679068286399239</v>
+        <v>3.537565659999268</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1210478417016917</v>
+        <v>0.1215280681959919</v>
       </c>
       <c r="C28">
-        <v>40.1738992052697</v>
+        <v>39.398753853842</v>
       </c>
       <c r="D28">
-        <v>42.1740992052697</v>
+        <v>41.90665385384201</v>
       </c>
       <c r="E28">
-        <v>6.630199999999999</v>
+        <v>7.137900000000001</v>
       </c>
       <c r="F28">
-        <v>13.2002</v>
+        <v>13.7079</v>
       </c>
       <c r="G28">
         <v>11.2</v>
@@ -3717,45 +3717,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M28">
-        <v>0.8091722600000001</v>
+        <v>0.8786763900000002</v>
       </c>
       <c r="N28">
-        <v>2.053327739999999</v>
+        <v>1.983823609999999</v>
       </c>
       <c r="O28">
-        <v>0.4106655479999999</v>
+        <v>0.3967647219999998</v>
       </c>
       <c r="P28">
-        <v>1.642662192</v>
+        <v>1.587058887999999</v>
       </c>
       <c r="Q28">
-        <v>2.792662191999999</v>
+        <v>2.737058887999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1463478941914753</v>
+        <v>0.1475102304054684</v>
       </c>
       <c r="T28">
-        <v>1.101040653557877</v>
+        <v>1.113768711514733</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.537565659999268</v>
+        <v>3.25774088455933</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1215280681959919</v>
+        <v>0.1214258946902922</v>
       </c>
       <c r="C29">
-        <v>39.398753853842</v>
+        <v>38.94767136235452</v>
       </c>
       <c r="D29">
-        <v>41.90665385384201</v>
+        <v>41.96327136235453</v>
       </c>
       <c r="E29">
-        <v>7.137900000000001</v>
+        <v>7.645600000000001</v>
       </c>
       <c r="F29">
-        <v>13.7079</v>
+        <v>14.2156</v>
       </c>
       <c r="G29">
         <v>11.2</v>
@@ -3799,28 +3799,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M29">
-        <v>0.8786763900000002</v>
+        <v>0.9112199600000002</v>
       </c>
       <c r="N29">
-        <v>1.983823609999999</v>
+        <v>1.951280039999999</v>
       </c>
       <c r="O29">
-        <v>0.3967647219999998</v>
+        <v>0.3902560079999999</v>
       </c>
       <c r="P29">
-        <v>1.587058887999999</v>
+        <v>1.561024031999999</v>
       </c>
       <c r="Q29">
-        <v>2.737058887999999</v>
+        <v>2.711024031999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1475102304054684</v>
+        <v>0.1487048537365169</v>
       </c>
       <c r="T29">
-        <v>1.113768711514733</v>
+        <v>1.126850326637058</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.25774088455933</v>
+        <v>3.141392995825068</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1214258946902922</v>
+        <v>0.1213237211845924</v>
       </c>
       <c r="C30">
-        <v>38.94767136235452</v>
+        <v>38.49674206271823</v>
       </c>
       <c r="D30">
-        <v>41.96327136235453</v>
+        <v>42.02004206271824</v>
       </c>
       <c r="E30">
-        <v>7.645600000000001</v>
+        <v>8.153300000000002</v>
       </c>
       <c r="F30">
-        <v>14.2156</v>
+        <v>14.7233</v>
       </c>
       <c r="G30">
         <v>11.2</v>
@@ -3881,28 +3881,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M30">
-        <v>0.9112199600000002</v>
+        <v>0.9437635300000001</v>
       </c>
       <c r="N30">
-        <v>1.951280039999999</v>
+        <v>1.918736469999999</v>
       </c>
       <c r="O30">
-        <v>0.3902560079999999</v>
+        <v>0.3837472939999999</v>
       </c>
       <c r="P30">
-        <v>1.561024031999999</v>
+        <v>1.534989175999999</v>
       </c>
       <c r="Q30">
-        <v>2.711024031999999</v>
+        <v>2.684989175999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1487048537365169</v>
+        <v>0.1499331284290034</v>
       </c>
       <c r="T30">
-        <v>1.126850326637058</v>
+        <v>1.140300437960011</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.141392995825068</v>
+        <v>3.033069099417308</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1213237211845924</v>
+        <v>0.1230935476788926</v>
       </c>
       <c r="C31">
-        <v>38.49674206271823</v>
+        <v>37.0268895161284</v>
       </c>
       <c r="D31">
-        <v>42.02004206271824</v>
+        <v>41.0578895161284</v>
       </c>
       <c r="E31">
-        <v>8.153299999999998</v>
+        <v>8.660999999999998</v>
       </c>
       <c r="F31">
-        <v>14.7233</v>
+        <v>15.231</v>
       </c>
       <c r="G31">
         <v>11.2</v>
@@ -3963,45 +3963,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M31">
-        <v>0.94376353</v>
+        <v>1.0951089</v>
       </c>
       <c r="N31">
-        <v>1.918736469999999</v>
+        <v>1.767391099999999</v>
       </c>
       <c r="O31">
-        <v>0.3837472939999999</v>
+        <v>0.3534782199999999</v>
       </c>
       <c r="P31">
-        <v>1.534989175999999</v>
+        <v>1.413912879999999</v>
       </c>
       <c r="Q31">
-        <v>2.684989175999999</v>
+        <v>2.563912879999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1499331284290034</v>
+        <v>0.1511964966841323</v>
       </c>
       <c r="T31">
-        <v>1.140300437960011</v>
+        <v>1.154134838177907</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.2</v>
       </c>
       <c r="W31">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.033069099417308</v>
+        <v>2.613895293883557</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1230935476788926</v>
+        <v>0.1230537741731928</v>
       </c>
       <c r="C32">
-        <v>37.0268895161284</v>
+        <v>36.54032785170059</v>
       </c>
       <c r="D32">
-        <v>41.0578895161284</v>
+        <v>41.07902785170059</v>
       </c>
       <c r="E32">
-        <v>8.660999999999998</v>
+        <v>9.168700000000001</v>
       </c>
       <c r="F32">
-        <v>15.231</v>
+        <v>15.7387</v>
       </c>
       <c r="G32">
         <v>11.2</v>
@@ -4045,28 +4045,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M32">
-        <v>1.0951089</v>
+        <v>1.13161253</v>
       </c>
       <c r="N32">
-        <v>1.767391099999999</v>
+        <v>1.730887469999999</v>
       </c>
       <c r="O32">
-        <v>0.3534782199999999</v>
+        <v>0.3461774939999999</v>
       </c>
       <c r="P32">
-        <v>1.413912879999999</v>
+        <v>1.384709975999999</v>
       </c>
       <c r="Q32">
-        <v>2.563912879999999</v>
+        <v>2.534709975999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1511964966841323</v>
+        <v>0.1524964843089751</v>
       </c>
       <c r="T32">
-        <v>1.154134838177907</v>
+        <v>1.168370235503567</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.613895293883557</v>
+        <v>2.529576090855056</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1230537741731928</v>
+        <v>0.1240124006674931</v>
       </c>
       <c r="C33">
-        <v>36.54032785170059</v>
+        <v>35.52913423530908</v>
       </c>
       <c r="D33">
-        <v>41.07902785170059</v>
+        <v>40.57553423530909</v>
       </c>
       <c r="E33">
-        <v>9.168700000000001</v>
+        <v>9.676400000000001</v>
       </c>
       <c r="F33">
-        <v>15.7387</v>
+        <v>16.2464</v>
       </c>
       <c r="G33">
         <v>11.2</v>
@@ -4127,45 +4127,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M33">
-        <v>1.13161253</v>
+        <v>1.23147712</v>
       </c>
       <c r="N33">
-        <v>1.730887469999999</v>
+        <v>1.631022879999999</v>
       </c>
       <c r="O33">
-        <v>0.3461774939999999</v>
+        <v>0.3262045759999999</v>
       </c>
       <c r="P33">
-        <v>1.384709975999999</v>
+        <v>1.304818303999999</v>
       </c>
       <c r="Q33">
-        <v>2.534709975999999</v>
+        <v>2.454818303999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1524964843089751</v>
+        <v>0.1538347068639604</v>
       </c>
       <c r="T33">
-        <v>1.168370235503567</v>
+        <v>1.183024320985864</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.2</v>
       </c>
       <c r="W33">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.529576090855056</v>
+        <v>2.324444322603411</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1240124006674931</v>
+        <v>0.1240038271617933</v>
       </c>
       <c r="C34">
-        <v>35.52913423530908</v>
+        <v>35.02588254157059</v>
       </c>
       <c r="D34">
-        <v>40.57553423530909</v>
+        <v>40.57998254157059</v>
       </c>
       <c r="E34">
-        <v>9.676400000000001</v>
+        <v>10.1841</v>
       </c>
       <c r="F34">
-        <v>16.2464</v>
+        <v>16.7541</v>
       </c>
       <c r="G34">
         <v>11.2</v>
@@ -4209,28 +4209,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M34">
-        <v>1.23147712</v>
+        <v>1.26996078</v>
       </c>
       <c r="N34">
-        <v>1.631022879999999</v>
+        <v>1.592539219999999</v>
       </c>
       <c r="O34">
-        <v>0.3262045759999999</v>
+        <v>0.3185078439999999</v>
       </c>
       <c r="P34">
-        <v>1.304818303999999</v>
+        <v>1.274031375999999</v>
       </c>
       <c r="Q34">
-        <v>2.454818303999999</v>
+        <v>2.424031375999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1538347068639604</v>
+        <v>0.1552128763608855</v>
       </c>
       <c r="T34">
-        <v>1.183024320985864</v>
+        <v>1.198115841855693</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.324444322603411</v>
+        <v>2.254006615857853</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1240038271617933</v>
+        <v>0.1239952536560935</v>
       </c>
       <c r="C35">
-        <v>35.02588254157059</v>
+        <v>34.52263182327697</v>
       </c>
       <c r="D35">
-        <v>40.57998254157059</v>
+        <v>40.58443182327697</v>
       </c>
       <c r="E35">
-        <v>10.1841</v>
+        <v>10.6918</v>
       </c>
       <c r="F35">
-        <v>16.7541</v>
+        <v>17.2618</v>
       </c>
       <c r="G35">
         <v>11.2</v>
@@ -4291,28 +4291,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M35">
-        <v>1.26996078</v>
+        <v>1.30844444</v>
       </c>
       <c r="N35">
-        <v>1.592539219999999</v>
+        <v>1.554055559999999</v>
       </c>
       <c r="O35">
-        <v>0.3185078439999999</v>
+        <v>0.3108111119999999</v>
       </c>
       <c r="P35">
-        <v>1.274031375999999</v>
+        <v>1.243244447999999</v>
       </c>
       <c r="Q35">
-        <v>2.424031375999999</v>
+        <v>2.393244447999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1552128763608855</v>
+        <v>0.1566328085698387</v>
       </c>
       <c r="T35">
-        <v>1.198115841855693</v>
+        <v>1.213664681539759</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.254006615857853</v>
+        <v>2.187712303626739</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1239952536560935</v>
+        <v>0.1239866801503938</v>
       </c>
       <c r="C36">
-        <v>34.52263182327697</v>
+        <v>34.01938208074905</v>
       </c>
       <c r="D36">
-        <v>40.58443182327697</v>
+        <v>40.58888208074907</v>
       </c>
       <c r="E36">
-        <v>10.6918</v>
+        <v>11.1995</v>
       </c>
       <c r="F36">
-        <v>17.2618</v>
+        <v>17.7695</v>
       </c>
       <c r="G36">
         <v>11.2</v>
@@ -4373,28 +4373,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M36">
-        <v>1.30844444</v>
+        <v>1.3469281</v>
       </c>
       <c r="N36">
-        <v>1.554055559999999</v>
+        <v>1.515571899999999</v>
       </c>
       <c r="O36">
-        <v>0.3108111119999999</v>
+        <v>0.3031143799999998</v>
       </c>
       <c r="P36">
-        <v>1.243244447999999</v>
+        <v>1.212457519999999</v>
       </c>
       <c r="Q36">
-        <v>2.393244447999999</v>
+        <v>2.362457519999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1566328085698387</v>
+        <v>0.1580964310006058</v>
       </c>
       <c r="T36">
-        <v>1.213664681539759</v>
+        <v>1.229691947060257</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.187712303626739</v>
+        <v>2.125206237808832</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1239866801503938</v>
+        <v>0.123978106644694</v>
       </c>
       <c r="C37">
-        <v>34.01938208074905</v>
+        <v>33.51613331430795</v>
       </c>
       <c r="D37">
-        <v>40.58888208074907</v>
+        <v>40.59333331430796</v>
       </c>
       <c r="E37">
-        <v>11.1995</v>
+        <v>11.7072</v>
       </c>
       <c r="F37">
-        <v>17.7695</v>
+        <v>18.2772</v>
       </c>
       <c r="G37">
         <v>11.2</v>
@@ -4455,28 +4455,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M37">
-        <v>1.3469281</v>
+        <v>1.38541176</v>
       </c>
       <c r="N37">
-        <v>1.515571899999999</v>
+        <v>1.477088239999999</v>
       </c>
       <c r="O37">
-        <v>0.3031143799999998</v>
+        <v>0.2954176479999998</v>
       </c>
       <c r="P37">
-        <v>1.212457519999999</v>
+        <v>1.181670591999999</v>
       </c>
       <c r="Q37">
-        <v>2.362457519999999</v>
+        <v>2.331670591999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1580964310006058</v>
+        <v>0.1596057916323344</v>
       </c>
       <c r="T37">
-        <v>1.229691947060257</v>
+        <v>1.246220064628272</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.125206237808832</v>
+        <v>2.066172731203031</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.123978106644694</v>
+        <v>0.1239695331389942</v>
       </c>
       <c r="C38">
-        <v>33.51613331430796</v>
+        <v>33.01288552427476</v>
       </c>
       <c r="D38">
-        <v>40.59333331430796</v>
+        <v>40.59778552427476</v>
       </c>
       <c r="E38">
-        <v>11.7072</v>
+        <v>12.2149</v>
       </c>
       <c r="F38">
-        <v>18.2772</v>
+        <v>18.7849</v>
       </c>
       <c r="G38">
         <v>11.2</v>
@@ -4537,28 +4537,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M38">
-        <v>1.38541176</v>
+        <v>1.42389542</v>
       </c>
       <c r="N38">
-        <v>1.477088239999999</v>
+        <v>1.438604579999999</v>
       </c>
       <c r="O38">
-        <v>0.2954176479999999</v>
+        <v>0.2877209159999998</v>
       </c>
       <c r="P38">
-        <v>1.181670591999999</v>
+        <v>1.150883663999999</v>
       </c>
       <c r="Q38">
-        <v>2.331670591999999</v>
+        <v>2.300883663999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1596057916323343</v>
+        <v>0.161163068474594</v>
       </c>
       <c r="T38">
-        <v>1.246220064628272</v>
+        <v>1.263272884341302</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.066172731203031</v>
+        <v>2.010330224954301</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1239695331389942</v>
+        <v>0.1282777596332945</v>
       </c>
       <c r="C39">
-        <v>33.01288552427476</v>
+        <v>30.38455984308211</v>
       </c>
       <c r="D39">
-        <v>40.59778552427476</v>
+        <v>38.47715984308211</v>
       </c>
       <c r="E39">
-        <v>12.2149</v>
+        <v>12.7226</v>
       </c>
       <c r="F39">
-        <v>18.7849</v>
+        <v>19.2926</v>
       </c>
       <c r="G39">
         <v>11.2</v>
@@ -4619,45 +4619,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M39">
-        <v>1.42389542</v>
+        <v>1.736334</v>
       </c>
       <c r="N39">
-        <v>1.438604579999999</v>
+        <v>1.126165999999999</v>
       </c>
       <c r="O39">
-        <v>0.2877209159999998</v>
+        <v>0.2252331999999999</v>
       </c>
       <c r="P39">
-        <v>1.150883663999999</v>
+        <v>0.9009327999999994</v>
       </c>
       <c r="Q39">
-        <v>2.300883663999999</v>
+        <v>2.050932799999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.161163068474594</v>
+        <v>0.1627705800537007</v>
       </c>
       <c r="T39">
-        <v>1.263272884341302</v>
+        <v>1.280875795012818</v>
       </c>
       <c r="U39">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V39">
         <v>0.2</v>
       </c>
       <c r="W39">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.010330224954301</v>
+        <v>1.648588347633577</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1282777596332945</v>
+        <v>0.1283827861275947</v>
       </c>
       <c r="C40">
-        <v>30.38455984308211</v>
+        <v>29.82792565959858</v>
       </c>
       <c r="D40">
-        <v>38.47715984308211</v>
+        <v>38.42822565959859</v>
       </c>
       <c r="E40">
-        <v>12.7226</v>
+        <v>13.2303</v>
       </c>
       <c r="F40">
-        <v>19.2926</v>
+        <v>19.8003</v>
       </c>
       <c r="G40">
         <v>11.2</v>
@@ -4701,28 +4701,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M40">
-        <v>1.736334</v>
+        <v>1.782027</v>
       </c>
       <c r="N40">
-        <v>1.126165999999999</v>
+        <v>1.080472999999999</v>
       </c>
       <c r="O40">
-        <v>0.2252331999999999</v>
+        <v>0.2160945999999998</v>
       </c>
       <c r="P40">
-        <v>0.9009327999999994</v>
+        <v>0.8643783999999993</v>
       </c>
       <c r="Q40">
-        <v>2.050932799999999</v>
+        <v>2.014378399999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1627705800537007</v>
+        <v>0.1644307969304831</v>
       </c>
       <c r="T40">
-        <v>1.280875795012818</v>
+        <v>1.299055850296514</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.648588347633577</v>
+        <v>1.606316851540408</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1283827861275947</v>
+        <v>0.1284878126218949</v>
       </c>
       <c r="C41">
-        <v>29.82792565959858</v>
+        <v>29.27141578429495</v>
       </c>
       <c r="D41">
-        <v>38.42822565959859</v>
+        <v>38.37941578429495</v>
       </c>
       <c r="E41">
-        <v>13.2303</v>
+        <v>13.738</v>
       </c>
       <c r="F41">
-        <v>19.8003</v>
+        <v>20.308</v>
       </c>
       <c r="G41">
         <v>11.2</v>
@@ -4783,28 +4783,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M41">
-        <v>1.782027</v>
+        <v>1.82772</v>
       </c>
       <c r="N41">
-        <v>1.080472999999999</v>
+        <v>1.034779999999999</v>
       </c>
       <c r="O41">
-        <v>0.2160945999999998</v>
+        <v>0.2069559999999998</v>
       </c>
       <c r="P41">
-        <v>0.8643783999999993</v>
+        <v>0.8278239999999993</v>
       </c>
       <c r="Q41">
-        <v>2.014378399999999</v>
+        <v>1.977823999999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1644307969304831</v>
+        <v>0.1661463543698249</v>
       </c>
       <c r="T41">
-        <v>1.299055850296514</v>
+        <v>1.317841907423</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.606316851540408</v>
+        <v>1.566158930251898</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1284878126218949</v>
+        <v>0.1285928391161952</v>
       </c>
       <c r="C42">
-        <v>29.27141578429495</v>
+        <v>28.71502974409939</v>
       </c>
       <c r="D42">
-        <v>38.37941578429495</v>
+        <v>38.33072974409939</v>
       </c>
       <c r="E42">
-        <v>13.738</v>
+        <v>14.2457</v>
       </c>
       <c r="F42">
-        <v>20.308</v>
+        <v>20.8157</v>
       </c>
       <c r="G42">
         <v>11.2</v>
@@ -4865,28 +4865,28 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M42">
-        <v>1.82772</v>
+        <v>1.873413</v>
       </c>
       <c r="N42">
-        <v>1.034779999999999</v>
+        <v>0.9890869999999992</v>
       </c>
       <c r="O42">
-        <v>0.2069559999999998</v>
+        <v>0.1978173999999998</v>
       </c>
       <c r="P42">
-        <v>0.8278239999999993</v>
+        <v>0.7912695999999994</v>
       </c>
       <c r="Q42">
-        <v>1.977823999999999</v>
+        <v>1.941269599999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1661463543698249</v>
+        <v>0.1679200662986358</v>
       </c>
       <c r="T42">
-        <v>1.317841907423</v>
+        <v>1.337264780045299</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.566158930251898</v>
+        <v>1.527959931953071</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1285928391161952</v>
+        <v>0.1494015008684705</v>
       </c>
       <c r="C43">
-        <v>28.71502974409939</v>
+        <v>20.50849156823678</v>
       </c>
       <c r="D43">
-        <v>38.33072974409939</v>
+        <v>30.63189156823678</v>
       </c>
       <c r="E43">
-        <v>14.2457</v>
+        <v>14.7534</v>
       </c>
       <c r="F43">
-        <v>20.8157</v>
+        <v>21.3234</v>
       </c>
       <c r="G43">
         <v>11.2</v>
@@ -4947,45 +4947,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M43">
-        <v>1.873413</v>
+        <v>3.130275120000001</v>
       </c>
       <c r="N43">
-        <v>0.9890869999999992</v>
+        <v>-0.2677751200000014</v>
       </c>
       <c r="O43">
-        <v>0.1978173999999998</v>
+        <v>-0.05355502400000028</v>
       </c>
       <c r="P43">
-        <v>0.7912695999999994</v>
+        <v>-0.2142200960000011</v>
       </c>
       <c r="Q43">
-        <v>1.941269599999999</v>
+        <v>0.9357799039999988</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1679200662986358</v>
+        <v>0.170727319252214</v>
       </c>
       <c r="T43">
-        <v>1.337264780045299</v>
+        <v>1.368005350512384</v>
       </c>
       <c r="U43">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V43">
-        <v>0.2</v>
+        <v>0.1828912725089799</v>
       </c>
       <c r="W43">
-        <v>0.07199999999999999</v>
+        <v>0.1199515611956817</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.527959931953071</v>
+        <v>0.9144563625448995</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1494015008684705</v>
+        <v>0.1504115008684705</v>
       </c>
       <c r="C44">
-        <v>20.50849156823678</v>
+        <v>19.70504769469444</v>
       </c>
       <c r="D44">
-        <v>30.63189156823678</v>
+        <v>30.33614769469444</v>
       </c>
       <c r="E44">
-        <v>14.7534</v>
+        <v>15.2611</v>
       </c>
       <c r="F44">
-        <v>21.3234</v>
+        <v>21.8311</v>
       </c>
       <c r="G44">
         <v>11.2</v>
@@ -5029,37 +5029,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M44">
-        <v>3.13027512</v>
+        <v>3.20480548</v>
       </c>
       <c r="N44">
-        <v>-0.2677751200000009</v>
+        <v>-0.3423054800000007</v>
       </c>
       <c r="O44">
-        <v>-0.05355502400000019</v>
+        <v>-0.06846109600000015</v>
       </c>
       <c r="P44">
-        <v>-0.2142200960000007</v>
+        <v>-0.2738443840000006</v>
       </c>
       <c r="Q44">
-        <v>0.9357799039999992</v>
+        <v>0.8761556159999994</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.170727319252214</v>
+        <v>0.172919026607516</v>
       </c>
       <c r="T44">
-        <v>1.368005350512384</v>
+        <v>1.392005444381022</v>
       </c>
       <c r="U44">
         <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.1828912725089799</v>
+        <v>0.1786379871017943</v>
       </c>
       <c r="W44">
-        <v>0.1199515611956817</v>
+        <v>0.1205759434934566</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9144563625448996</v>
+        <v>0.8931899355089717</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1504115008684705</v>
+        <v>0.1514215008684705</v>
       </c>
       <c r="C45">
-        <v>19.70504769469444</v>
+        <v>18.90725989136169</v>
       </c>
       <c r="D45">
-        <v>30.33614769469444</v>
+        <v>30.0460598913617</v>
       </c>
       <c r="E45">
-        <v>15.2611</v>
+        <v>15.7688</v>
       </c>
       <c r="F45">
-        <v>21.8311</v>
+        <v>22.3388</v>
       </c>
       <c r="G45">
         <v>11.2</v>
@@ -5111,37 +5111,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M45">
-        <v>3.20480548</v>
+        <v>3.279335840000001</v>
       </c>
       <c r="N45">
-        <v>-0.3423054800000007</v>
+        <v>-0.4168358400000014</v>
       </c>
       <c r="O45">
-        <v>-0.06846109600000015</v>
+        <v>-0.08336716800000028</v>
       </c>
       <c r="P45">
-        <v>-0.2738443840000006</v>
+        <v>-0.3334686720000011</v>
       </c>
       <c r="Q45">
-        <v>0.8761556159999994</v>
+        <v>0.8165313279999988</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.172919026607516</v>
+        <v>0.1751890092255074</v>
       </c>
       <c r="T45">
-        <v>1.392005444381022</v>
+        <v>1.416862684459255</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1786379871017943</v>
+        <v>0.1745780328494808</v>
       </c>
       <c r="W45">
-        <v>0.1205759434934566</v>
+        <v>0.1211719447776962</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8931899355089717</v>
+        <v>0.8728901642474041</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1514215008684705</v>
+        <v>0.1524315008684705</v>
       </c>
       <c r="C46">
-        <v>18.90725989136169</v>
+        <v>18.11496743750787</v>
       </c>
       <c r="D46">
-        <v>30.0460598913617</v>
+        <v>29.76146743750787</v>
       </c>
       <c r="E46">
-        <v>15.7688</v>
+        <v>16.2765</v>
       </c>
       <c r="F46">
-        <v>22.3388</v>
+        <v>22.8465</v>
       </c>
       <c r="G46">
         <v>11.2</v>
@@ -5193,37 +5193,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M46">
-        <v>3.279335840000001</v>
+        <v>3.353866200000001</v>
       </c>
       <c r="N46">
-        <v>-0.4168358400000014</v>
+        <v>-0.4913662000000012</v>
       </c>
       <c r="O46">
-        <v>-0.08336716800000028</v>
+        <v>-0.09827324000000025</v>
       </c>
       <c r="P46">
-        <v>-0.3334686720000011</v>
+        <v>-0.3930929600000009</v>
       </c>
       <c r="Q46">
-        <v>0.8165313279999988</v>
+        <v>0.756907039999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1751890092255074</v>
+        <v>0.1775415366659712</v>
       </c>
       <c r="T46">
-        <v>1.416862684459255</v>
+        <v>1.442623824176696</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1745780328494808</v>
+        <v>0.1706985210083813</v>
       </c>
       <c r="W46">
-        <v>0.1211719447776962</v>
+        <v>0.1217414571159696</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8728901642474041</v>
+        <v>0.8534926050419063</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1524315008684705</v>
+        <v>0.1534415008684705</v>
       </c>
       <c r="C47">
-        <v>18.11496743750787</v>
+        <v>17.32801564457148</v>
       </c>
       <c r="D47">
-        <v>29.76146743750787</v>
+        <v>29.48221564457149</v>
       </c>
       <c r="E47">
-        <v>16.2765</v>
+        <v>16.7842</v>
       </c>
       <c r="F47">
-        <v>22.8465</v>
+        <v>23.3542</v>
       </c>
       <c r="G47">
         <v>11.2</v>
@@ -5275,37 +5275,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M47">
-        <v>3.353866200000001</v>
+        <v>3.428396560000001</v>
       </c>
       <c r="N47">
-        <v>-0.4913662000000012</v>
+        <v>-0.5658965600000014</v>
       </c>
       <c r="O47">
-        <v>-0.09827324000000025</v>
+        <v>-0.1131793120000003</v>
       </c>
       <c r="P47">
-        <v>-0.3930929600000009</v>
+        <v>-0.4527172480000011</v>
       </c>
       <c r="Q47">
-        <v>0.756907039999999</v>
+        <v>0.6972827519999988</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1775415366659712</v>
+        <v>0.179981194752378</v>
       </c>
       <c r="T47">
-        <v>1.442623824176696</v>
+        <v>1.469339080179968</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1706985210083813</v>
+        <v>0.1669876835951556</v>
       </c>
       <c r="W47">
-        <v>0.1217414571159696</v>
+        <v>0.1222862080482312</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8534926050419063</v>
+        <v>0.8349384179757777</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1534415008684705</v>
+        <v>0.1544515008684705</v>
       </c>
       <c r="C48">
-        <v>17.32801564457148</v>
+        <v>16.54625557579191</v>
       </c>
       <c r="D48">
-        <v>29.48221564457149</v>
+        <v>29.20815557579192</v>
       </c>
       <c r="E48">
-        <v>16.7842</v>
+        <v>17.2919</v>
       </c>
       <c r="F48">
-        <v>23.3542</v>
+        <v>23.8619</v>
       </c>
       <c r="G48">
         <v>11.2</v>
@@ -5357,37 +5357,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M48">
-        <v>3.428396560000001</v>
+        <v>3.502926920000001</v>
       </c>
       <c r="N48">
-        <v>-0.5658965600000014</v>
+        <v>-0.6404269200000012</v>
       </c>
       <c r="O48">
-        <v>-0.1131793120000003</v>
+        <v>-0.1280853840000002</v>
       </c>
       <c r="P48">
-        <v>-0.4527172480000011</v>
+        <v>-0.512341536000001</v>
       </c>
       <c r="Q48">
-        <v>0.6972827519999988</v>
+        <v>0.6376584639999989</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.179981194752378</v>
+        <v>0.1825129154080833</v>
       </c>
       <c r="T48">
-        <v>1.469339080179968</v>
+        <v>1.497062459051288</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1669876835951556</v>
+        <v>0.1634347541569608</v>
       </c>
       <c r="W48">
-        <v>0.1222862080482312</v>
+        <v>0.1228077780897582</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8349384179757777</v>
+        <v>0.8171737707848038</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1544515008684705</v>
+        <v>0.1554615008684705</v>
       </c>
       <c r="C49">
-        <v>16.54625557579191</v>
+        <v>15.76954378133423</v>
       </c>
       <c r="D49">
-        <v>29.20815557579192</v>
+        <v>28.93914378133423</v>
       </c>
       <c r="E49">
-        <v>17.2919</v>
+        <v>17.7996</v>
       </c>
       <c r="F49">
-        <v>23.8619</v>
+        <v>24.3696</v>
       </c>
       <c r="G49">
         <v>11.2</v>
@@ -5439,37 +5439,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M49">
-        <v>3.502926920000001</v>
+        <v>3.57745728</v>
       </c>
       <c r="N49">
-        <v>-0.6404269200000012</v>
+        <v>-0.714957280000001</v>
       </c>
       <c r="O49">
-        <v>-0.1280853840000002</v>
+        <v>-0.1429914560000002</v>
       </c>
       <c r="P49">
-        <v>-0.512341536000001</v>
+        <v>-0.5719658240000008</v>
       </c>
       <c r="Q49">
-        <v>0.6376584639999989</v>
+        <v>0.5780341759999991</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1825129154080833</v>
+        <v>0.1851420099351618</v>
       </c>
       <c r="T49">
-        <v>1.497062459051288</v>
+        <v>1.525852121725351</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1634347541569608</v>
+        <v>0.1600298634453574</v>
       </c>
       <c r="W49">
-        <v>0.1228077780897582</v>
+        <v>0.1233076160462215</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8171737707848038</v>
+        <v>0.8001493172267872</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1554615008684705</v>
+        <v>0.1845528206638614</v>
       </c>
       <c r="C50">
-        <v>15.76954378133423</v>
+        <v>9.194378757418779</v>
       </c>
       <c r="D50">
-        <v>28.93914378133423</v>
+        <v>22.87167875741878</v>
       </c>
       <c r="E50">
-        <v>17.7996</v>
+        <v>18.3073</v>
       </c>
       <c r="F50">
-        <v>24.3696</v>
+        <v>24.8773</v>
       </c>
       <c r="G50">
         <v>11.2</v>
@@ -5521,45 +5521,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M50">
-        <v>3.57745728</v>
+        <v>4.99536184</v>
       </c>
       <c r="N50">
-        <v>-0.714957280000001</v>
+        <v>-2.132861840000001</v>
       </c>
       <c r="O50">
-        <v>-0.1429914560000002</v>
+        <v>-0.4265723680000002</v>
       </c>
       <c r="P50">
-        <v>-0.5719658240000008</v>
+        <v>-1.706289472000001</v>
       </c>
       <c r="Q50">
-        <v>0.5780341759999991</v>
+        <v>-0.5562894720000007</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1851420099351618</v>
+        <v>0.1910532646307353</v>
       </c>
       <c r="T50">
-        <v>1.525852121725351</v>
+        <v>1.590582783522872</v>
       </c>
       <c r="U50">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1600298634453574</v>
+        <v>0.1146063124828611</v>
       </c>
       <c r="W50">
-        <v>0.1233076160462215</v>
+        <v>0.1777870524534415</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8001493172267872</v>
+        <v>0.5730315624143054</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1845528206638614</v>
+        <v>0.1861028206638614</v>
       </c>
       <c r="C51">
-        <v>9.194378757418779</v>
+        <v>8.434003138309652</v>
       </c>
       <c r="D51">
-        <v>22.87167875741878</v>
+        <v>22.61900313830965</v>
       </c>
       <c r="E51">
-        <v>18.3073</v>
+        <v>18.815</v>
       </c>
       <c r="F51">
-        <v>24.8773</v>
+        <v>25.385</v>
       </c>
       <c r="G51">
         <v>11.2</v>
@@ -5603,37 +5603,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M51">
-        <v>4.99536184</v>
+        <v>5.097308000000001</v>
       </c>
       <c r="N51">
-        <v>-2.132861840000001</v>
+        <v>-2.234808000000001</v>
       </c>
       <c r="O51">
-        <v>-0.4265723680000002</v>
+        <v>-0.4469616000000003</v>
       </c>
       <c r="P51">
-        <v>-1.706289472000001</v>
+        <v>-1.787846400000001</v>
       </c>
       <c r="Q51">
-        <v>-0.5562894720000007</v>
+        <v>-0.6378464000000013</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1910532646307353</v>
+        <v>0.19395832992335</v>
       </c>
       <c r="T51">
-        <v>1.590582783522872</v>
+        <v>1.62239443919333</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1146063124828611</v>
+        <v>0.1123141862332038</v>
       </c>
       <c r="W51">
-        <v>0.1777870524534415</v>
+        <v>0.1782473114043727</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5730315624143054</v>
+        <v>0.5615709311660192</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1861028206638614</v>
+        <v>0.1876528206638614</v>
       </c>
       <c r="C52">
-        <v>8.434003138309652</v>
+        <v>7.679149400369834</v>
       </c>
       <c r="D52">
-        <v>22.61900313830965</v>
+        <v>22.37184940036984</v>
       </c>
       <c r="E52">
-        <v>18.815</v>
+        <v>19.3227</v>
       </c>
       <c r="F52">
-        <v>25.385</v>
+        <v>25.8927</v>
       </c>
       <c r="G52">
         <v>11.2</v>
@@ -5685,37 +5685,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M52">
-        <v>5.097308000000001</v>
+        <v>5.199254160000001</v>
       </c>
       <c r="N52">
-        <v>-2.234808000000001</v>
+        <v>-2.336754160000001</v>
       </c>
       <c r="O52">
-        <v>-0.4469616000000003</v>
+        <v>-0.4673508320000003</v>
       </c>
       <c r="P52">
-        <v>-1.787846400000001</v>
+        <v>-1.869403328000001</v>
       </c>
       <c r="Q52">
-        <v>-0.6378464000000013</v>
+        <v>-0.7194033280000012</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.19395832992335</v>
+        <v>0.1969819693095408</v>
       </c>
       <c r="T52">
-        <v>1.62239443919333</v>
+        <v>1.655504529789112</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1123141862332038</v>
+        <v>0.1101119472874548</v>
       </c>
       <c r="W52">
-        <v>0.1782473114043727</v>
+        <v>0.1786895209846791</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5615709311660192</v>
+        <v>0.5505597364372737</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1876528206638614</v>
+        <v>0.1892028206638613</v>
       </c>
       <c r="C53">
-        <v>7.679149400369834</v>
+        <v>6.929638490305134</v>
       </c>
       <c r="D53">
-        <v>22.37184940036984</v>
+        <v>22.13003849030514</v>
       </c>
       <c r="E53">
-        <v>19.3227</v>
+        <v>19.8304</v>
       </c>
       <c r="F53">
-        <v>25.8927</v>
+        <v>26.4004</v>
       </c>
       <c r="G53">
         <v>11.2</v>
@@ -5767,37 +5767,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M53">
-        <v>5.199254160000001</v>
+        <v>5.30120032</v>
       </c>
       <c r="N53">
-        <v>-2.336754160000001</v>
+        <v>-2.438700320000001</v>
       </c>
       <c r="O53">
-        <v>-0.4673508320000003</v>
+        <v>-0.4877400640000003</v>
       </c>
       <c r="P53">
-        <v>-1.869403328000001</v>
+        <v>-1.950960256000001</v>
       </c>
       <c r="Q53">
-        <v>-0.7194033280000012</v>
+        <v>-0.8009602560000009</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1969819693095408</v>
+        <v>0.2001315936701563</v>
       </c>
       <c r="T53">
-        <v>1.655504529789112</v>
+        <v>1.689994207493052</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1101119472874548</v>
+        <v>0.1079944098396191</v>
       </c>
       <c r="W53">
-        <v>0.1786895209846791</v>
+        <v>0.1791147225042045</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5505597364372737</v>
+        <v>0.5399720491980955</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1892028206638613</v>
+        <v>0.1907528206638613</v>
       </c>
       <c r="C54">
-        <v>6.929638490305134</v>
+        <v>6.185299013385148</v>
       </c>
       <c r="D54">
-        <v>22.13003849030514</v>
+        <v>21.89339901338515</v>
       </c>
       <c r="E54">
-        <v>19.8304</v>
+        <v>20.3381</v>
       </c>
       <c r="F54">
-        <v>26.4004</v>
+        <v>26.9081</v>
       </c>
       <c r="G54">
         <v>11.2</v>
@@ -5849,37 +5849,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M54">
-        <v>5.30120032</v>
+        <v>5.403146480000001</v>
       </c>
       <c r="N54">
-        <v>-2.438700320000001</v>
+        <v>-2.540646480000002</v>
       </c>
       <c r="O54">
-        <v>-0.4877400640000003</v>
+        <v>-0.5081292960000003</v>
       </c>
       <c r="P54">
-        <v>-1.950960256000001</v>
+        <v>-2.032517184000001</v>
       </c>
       <c r="Q54">
-        <v>-0.8009602560000009</v>
+        <v>-0.8825171840000015</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2001315936701563</v>
+        <v>0.2034152445993086</v>
       </c>
       <c r="T54">
-        <v>1.689994207493052</v>
+        <v>1.725951531056734</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1079944098396191</v>
+        <v>0.1059567794652866</v>
       </c>
       <c r="W54">
-        <v>0.1791147225042045</v>
+        <v>0.1795238786833704</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5399720491980955</v>
+        <v>0.5297838973264332</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1907528206638613</v>
+        <v>0.1923028206638613</v>
       </c>
       <c r="C55">
-        <v>6.185299013385148</v>
+        <v>5.445966828305188</v>
       </c>
       <c r="D55">
-        <v>21.89339901338515</v>
+        <v>21.66176682830519</v>
       </c>
       <c r="E55">
-        <v>20.3381</v>
+        <v>20.8458</v>
       </c>
       <c r="F55">
-        <v>26.9081</v>
+        <v>27.4158</v>
       </c>
       <c r="G55">
         <v>11.2</v>
@@ -5931,37 +5931,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M55">
-        <v>5.403146480000001</v>
+        <v>5.505092640000001</v>
       </c>
       <c r="N55">
-        <v>-2.540646480000002</v>
+        <v>-2.642592640000001</v>
       </c>
       <c r="O55">
-        <v>-0.5081292960000003</v>
+        <v>-0.5285185280000003</v>
       </c>
       <c r="P55">
-        <v>-2.032517184000001</v>
+        <v>-2.114074112000001</v>
       </c>
       <c r="Q55">
-        <v>-0.8825171840000015</v>
+        <v>-0.9640741120000014</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2034152445993086</v>
+        <v>0.2068416629601631</v>
       </c>
       <c r="T55">
-        <v>1.725951531056734</v>
+        <v>1.763472216514489</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1059567794652866</v>
+        <v>0.1039946168825961</v>
       </c>
       <c r="W55">
-        <v>0.1795238786833704</v>
+        <v>0.1799178809299747</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5297838973264332</v>
+        <v>0.5199730844129807</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1923028206638613</v>
+        <v>0.1938528206638614</v>
       </c>
       <c r="C56">
-        <v>5.445966828305188</v>
+        <v>4.71148466749716</v>
       </c>
       <c r="D56">
-        <v>21.66176682830519</v>
+        <v>21.43498466749717</v>
       </c>
       <c r="E56">
-        <v>20.8458</v>
+        <v>21.3535</v>
       </c>
       <c r="F56">
-        <v>27.4158</v>
+        <v>27.9235</v>
       </c>
       <c r="G56">
         <v>11.2</v>
@@ -6013,37 +6013,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M56">
-        <v>5.505092640000001</v>
+        <v>5.607038800000001</v>
       </c>
       <c r="N56">
-        <v>-2.642592640000001</v>
+        <v>-2.744538800000001</v>
       </c>
       <c r="O56">
-        <v>-0.5285185280000003</v>
+        <v>-0.5489077600000003</v>
       </c>
       <c r="P56">
-        <v>-2.114074112000001</v>
+        <v>-2.195631040000001</v>
       </c>
       <c r="Q56">
-        <v>-0.9640741120000014</v>
+        <v>-1.045631040000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2068416629601631</v>
+        <v>0.2104203665815001</v>
       </c>
       <c r="T56">
-        <v>1.763472216514489</v>
+        <v>1.802660487992589</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1039946168825961</v>
+        <v>0.102103805666549</v>
       </c>
       <c r="W56">
-        <v>0.1799178809299747</v>
+        <v>0.180297555822157</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5199730844129807</v>
+        <v>0.5105190283327448</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1938528206638614</v>
+        <v>0.1954028206638613</v>
       </c>
       <c r="C57">
-        <v>4.71148466749716</v>
+        <v>3.981701781043633</v>
       </c>
       <c r="D57">
-        <v>21.43498466749717</v>
+        <v>21.21290178104364</v>
       </c>
       <c r="E57">
-        <v>21.3535</v>
+        <v>21.8612</v>
       </c>
       <c r="F57">
-        <v>27.9235</v>
+        <v>28.4312</v>
       </c>
       <c r="G57">
         <v>11.2</v>
@@ -6095,37 +6095,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M57">
-        <v>5.607038800000001</v>
+        <v>5.708984960000001</v>
       </c>
       <c r="N57">
-        <v>-2.744538800000001</v>
+        <v>-2.846484960000002</v>
       </c>
       <c r="O57">
-        <v>-0.5489077600000003</v>
+        <v>-0.5692969920000004</v>
       </c>
       <c r="P57">
-        <v>-2.195631040000001</v>
+        <v>-2.277187968000002</v>
       </c>
       <c r="Q57">
-        <v>-1.045631040000001</v>
+        <v>-1.127187968000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2104203665815001</v>
+        <v>0.2141617385492614</v>
       </c>
       <c r="T57">
-        <v>1.802660487992589</v>
+        <v>1.843630044537875</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.102103805666549</v>
+        <v>0.1002805234225034</v>
       </c>
       <c r="W57">
-        <v>0.180297555822157</v>
+        <v>0.1806636708967613</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5105190283327448</v>
+        <v>0.5014026171125171</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1954028206638613</v>
+        <v>0.217557042784673</v>
       </c>
       <c r="C58">
-        <v>3.981701781043633</v>
+        <v>0.7378383593586726</v>
       </c>
       <c r="D58">
-        <v>21.21290178104364</v>
+        <v>18.47673835935868</v>
       </c>
       <c r="E58">
-        <v>21.8612</v>
+        <v>22.3689</v>
       </c>
       <c r="F58">
-        <v>28.4312</v>
+        <v>28.9389</v>
       </c>
       <c r="G58">
         <v>11.2</v>
@@ -6177,45 +6177,45 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M58">
-        <v>5.708984960000001</v>
+        <v>6.823792620000001</v>
       </c>
       <c r="N58">
-        <v>-2.846484960000002</v>
+        <v>-3.961292620000001</v>
       </c>
       <c r="O58">
-        <v>-0.5692969920000004</v>
+        <v>-0.7922585240000003</v>
       </c>
       <c r="P58">
-        <v>-2.277187968000002</v>
+        <v>-3.169034096000001</v>
       </c>
       <c r="Q58">
-        <v>-1.127187968000002</v>
+        <v>-2.019034096000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2141617385492614</v>
+        <v>0.2195985746104341</v>
       </c>
       <c r="T58">
-        <v>1.843630044537875</v>
+        <v>1.903165627835929</v>
       </c>
       <c r="U58">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1002805234225034</v>
+        <v>0.08389762583376982</v>
       </c>
       <c r="W58">
-        <v>0.1806636708967613</v>
+        <v>0.2160169398283971</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.5014026171125171</v>
+        <v>0.419488129168849</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.217557042784673</v>
+        <v>0.219457042784673</v>
       </c>
       <c r="C59">
-        <v>0.7378383593586726</v>
+        <v>0.02798241843141014</v>
       </c>
       <c r="D59">
-        <v>18.47673835935868</v>
+        <v>18.27458241843141</v>
       </c>
       <c r="E59">
-        <v>22.3689</v>
+        <v>22.8766</v>
       </c>
       <c r="F59">
-        <v>28.9389</v>
+        <v>29.4466</v>
       </c>
       <c r="G59">
         <v>11.2</v>
@@ -6259,37 +6259,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M59">
-        <v>6.823792620000001</v>
+        <v>6.943508280000001</v>
       </c>
       <c r="N59">
-        <v>-3.961292620000001</v>
+        <v>-4.081008280000002</v>
       </c>
       <c r="O59">
-        <v>-0.7922585240000003</v>
+        <v>-0.8162016560000005</v>
       </c>
       <c r="P59">
-        <v>-3.169034096000001</v>
+        <v>-3.264806624000002</v>
       </c>
       <c r="Q59">
-        <v>-2.019034096000001</v>
+        <v>-2.114806624000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2195985746104341</v>
+        <v>0.2237366359106825</v>
       </c>
       <c r="T59">
-        <v>1.903165627835929</v>
+        <v>1.948479095165356</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08389762583376982</v>
+        <v>0.08245111504353241</v>
       </c>
       <c r="W59">
-        <v>0.2160169398283971</v>
+        <v>0.2163580270727351</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.419488129168849</v>
+        <v>0.4122555752176619</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.219457042784673</v>
+        <v>0.221357042784673</v>
       </c>
       <c r="C60">
-        <v>0.02798241843141369</v>
+        <v>-0.6774977790717251</v>
       </c>
       <c r="D60">
-        <v>18.27458241843141</v>
+        <v>18.07680222092828</v>
       </c>
       <c r="E60">
-        <v>22.8766</v>
+        <v>23.3843</v>
       </c>
       <c r="F60">
-        <v>29.4466</v>
+        <v>29.9543</v>
       </c>
       <c r="G60">
         <v>11.2</v>
@@ -6341,37 +6341,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M60">
-        <v>6.943508280000001</v>
+        <v>7.06322394</v>
       </c>
       <c r="N60">
-        <v>-4.081008280000001</v>
+        <v>-4.200723940000001</v>
       </c>
       <c r="O60">
-        <v>-0.8162016560000002</v>
+        <v>-0.8401447880000004</v>
       </c>
       <c r="P60">
-        <v>-3.264806624000001</v>
+        <v>-3.360579152000001</v>
       </c>
       <c r="Q60">
-        <v>-2.114806624000001</v>
+        <v>-2.210579152000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2237366359106824</v>
+        <v>0.2280765538597235</v>
       </c>
       <c r="T60">
-        <v>1.948479095165356</v>
+        <v>1.996002975535242</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.08245111504353242</v>
+        <v>0.08105363851737085</v>
       </c>
       <c r="W60">
-        <v>0.2163580270727351</v>
+        <v>0.216687552037604</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4122555752176621</v>
+        <v>0.4052681925868542</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.221357042784673</v>
+        <v>0.223257042784673</v>
       </c>
       <c r="C61">
-        <v>-0.6774977790717251</v>
+        <v>-1.378742783996884</v>
       </c>
       <c r="D61">
-        <v>18.07680222092828</v>
+        <v>17.88325721600312</v>
       </c>
       <c r="E61">
-        <v>23.3843</v>
+        <v>23.892</v>
       </c>
       <c r="F61">
-        <v>29.9543</v>
+        <v>30.462</v>
       </c>
       <c r="G61">
         <v>11.2</v>
@@ -6423,37 +6423,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M61">
-        <v>7.06322394</v>
+        <v>7.1829396</v>
       </c>
       <c r="N61">
-        <v>-4.200723940000001</v>
+        <v>-4.3204396</v>
       </c>
       <c r="O61">
-        <v>-0.8401447880000004</v>
+        <v>-0.8640879200000001</v>
       </c>
       <c r="P61">
-        <v>-3.360579152000001</v>
+        <v>-3.45635168</v>
       </c>
       <c r="Q61">
-        <v>-2.210579152000001</v>
+        <v>-2.30635168</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2280765538597235</v>
+        <v>0.2326334677062165</v>
       </c>
       <c r="T61">
-        <v>1.996002975535242</v>
+        <v>2.045903049923623</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.08105363851737085</v>
+        <v>0.07970274454208133</v>
       </c>
       <c r="W61">
-        <v>0.216687552037604</v>
+        <v>0.2170060928369772</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4052681925868542</v>
+        <v>0.3985137227104067</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.223257042784673</v>
+        <v>0.225157042784673</v>
       </c>
       <c r="C62">
-        <v>-1.378742783996884</v>
+        <v>-2.075887191547686</v>
       </c>
       <c r="D62">
-        <v>17.88325721600312</v>
+        <v>17.69381280845231</v>
       </c>
       <c r="E62">
-        <v>23.892</v>
+        <v>24.3997</v>
       </c>
       <c r="F62">
-        <v>30.462</v>
+        <v>30.9697</v>
       </c>
       <c r="G62">
         <v>11.2</v>
@@ -6505,37 +6505,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M62">
-        <v>7.1829396</v>
+        <v>7.30265526</v>
       </c>
       <c r="N62">
-        <v>-4.3204396</v>
+        <v>-4.440155260000001</v>
       </c>
       <c r="O62">
-        <v>-0.8640879200000001</v>
+        <v>-0.8880310520000002</v>
       </c>
       <c r="P62">
-        <v>-3.45635168</v>
+        <v>-3.552124208000001</v>
       </c>
       <c r="Q62">
-        <v>-2.30635168</v>
+        <v>-2.402124208000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2326334677062165</v>
+        <v>0.2374240694422734</v>
       </c>
       <c r="T62">
-        <v>2.045903049923623</v>
+        <v>2.098362102485768</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07970274454208133</v>
+        <v>0.07839614217253903</v>
       </c>
       <c r="W62">
-        <v>0.2170060928369772</v>
+        <v>0.2173141896757153</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3985137227104067</v>
+        <v>0.391980710862695</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.225157042784673</v>
+        <v>0.227057042784673</v>
       </c>
       <c r="C63">
-        <v>-2.075887191547686</v>
+        <v>-2.769059953430915</v>
       </c>
       <c r="D63">
-        <v>17.69381280845231</v>
+        <v>17.50834004656909</v>
       </c>
       <c r="E63">
-        <v>24.3997</v>
+        <v>24.9074</v>
       </c>
       <c r="F63">
-        <v>30.9697</v>
+        <v>31.4774</v>
       </c>
       <c r="G63">
         <v>11.2</v>
@@ -6587,37 +6587,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M63">
-        <v>7.30265526</v>
+        <v>7.422370920000001</v>
       </c>
       <c r="N63">
-        <v>-4.440155260000001</v>
+        <v>-4.559870920000002</v>
       </c>
       <c r="O63">
-        <v>-0.8880310520000002</v>
+        <v>-0.9119741840000004</v>
       </c>
       <c r="P63">
-        <v>-3.552124208000001</v>
+        <v>-3.647896736000001</v>
       </c>
       <c r="Q63">
-        <v>-2.402124208000001</v>
+        <v>-2.497896736000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2374240694422734</v>
+        <v>0.2424668081118069</v>
       </c>
       <c r="T63">
-        <v>2.098362102485768</v>
+        <v>2.153582157814341</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07839614217253903</v>
+        <v>0.07713168826653032</v>
       </c>
       <c r="W63">
-        <v>0.2173141896757153</v>
+        <v>0.2176123479067522</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.391980710862695</v>
+        <v>0.3856584413326516</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.227057042784673</v>
+        <v>0.228957042784673</v>
       </c>
       <c r="C64">
-        <v>-2.769059953430915</v>
+        <v>-3.458384670573736</v>
       </c>
       <c r="D64">
-        <v>17.50834004656909</v>
+        <v>17.32671532942627</v>
       </c>
       <c r="E64">
-        <v>24.9074</v>
+        <v>25.4151</v>
       </c>
       <c r="F64">
-        <v>31.4774</v>
+        <v>31.9851</v>
       </c>
       <c r="G64">
         <v>11.2</v>
@@ -6669,37 +6669,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M64">
-        <v>7.422370920000001</v>
+        <v>7.542086580000001</v>
       </c>
       <c r="N64">
-        <v>-4.559870920000002</v>
+        <v>-4.679586580000002</v>
       </c>
       <c r="O64">
-        <v>-0.9119741840000004</v>
+        <v>-0.9359173160000005</v>
       </c>
       <c r="P64">
-        <v>-3.647896736000001</v>
+        <v>-3.743669264000002</v>
       </c>
       <c r="Q64">
-        <v>-2.497896736000001</v>
+        <v>-2.593669264000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2424668081118069</v>
+        <v>0.2477821272499638</v>
       </c>
       <c r="T64">
-        <v>2.153582157814341</v>
+        <v>2.211787080998512</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07713168826653032</v>
+        <v>0.07590737575436317</v>
       </c>
       <c r="W64">
-        <v>0.2176123479067522</v>
+        <v>0.2179010407971212</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3856584413326516</v>
+        <v>0.3795368787718157</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.228957042784673</v>
+        <v>0.230857042784673</v>
       </c>
       <c r="C65">
-        <v>-3.458384670573736</v>
+        <v>-4.143979867808756</v>
       </c>
       <c r="D65">
-        <v>17.32671532942627</v>
+        <v>17.14882013219125</v>
       </c>
       <c r="E65">
-        <v>25.4151</v>
+        <v>25.9228</v>
       </c>
       <c r="F65">
-        <v>31.9851</v>
+        <v>32.4928</v>
       </c>
       <c r="G65">
         <v>11.2</v>
@@ -6751,37 +6751,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M65">
-        <v>7.542086580000001</v>
+        <v>7.661802240000001</v>
       </c>
       <c r="N65">
-        <v>-4.679586580000002</v>
+        <v>-4.799302240000001</v>
       </c>
       <c r="O65">
-        <v>-0.9359173160000005</v>
+        <v>-0.9598604480000003</v>
       </c>
       <c r="P65">
-        <v>-3.743669264000002</v>
+        <v>-3.839441792000001</v>
       </c>
       <c r="Q65">
-        <v>-2.593669264000002</v>
+        <v>-2.689441792000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2477821272499638</v>
+        <v>0.2533927418957962</v>
       </c>
       <c r="T65">
-        <v>2.211787080998512</v>
+        <v>2.273225611026249</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07590737575436317</v>
+        <v>0.07472132300820125</v>
       </c>
       <c r="W65">
-        <v>0.2179010407971212</v>
+        <v>0.2181807120346662</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3795368787718157</v>
+        <v>0.3736066150410062</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.230857042784673</v>
+        <v>0.232757042784673</v>
       </c>
       <c r="C66">
-        <v>-4.143979867808756</v>
+        <v>-4.825959251809767</v>
       </c>
       <c r="D66">
-        <v>17.14882013219125</v>
+        <v>16.97454074819024</v>
       </c>
       <c r="E66">
-        <v>25.9228</v>
+        <v>26.4305</v>
       </c>
       <c r="F66">
-        <v>32.4928</v>
+        <v>33.0005</v>
       </c>
       <c r="G66">
         <v>11.2</v>
@@ -6833,37 +6833,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M66">
-        <v>7.661802240000001</v>
+        <v>7.781517900000001</v>
       </c>
       <c r="N66">
-        <v>-4.799302240000001</v>
+        <v>-4.919017900000002</v>
       </c>
       <c r="O66">
-        <v>-0.9598604480000003</v>
+        <v>-0.9838035800000005</v>
       </c>
       <c r="P66">
-        <v>-3.839441792000001</v>
+        <v>-3.935214320000001</v>
       </c>
       <c r="Q66">
-        <v>-2.689441792000001</v>
+        <v>-2.785214320000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2533927418957962</v>
+        <v>0.2593239630928189</v>
       </c>
       <c r="T66">
-        <v>2.273225611026249</v>
+        <v>2.338174914198427</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07472132300820125</v>
+        <v>0.07357176419269046</v>
       </c>
       <c r="W66">
-        <v>0.2181807120346662</v>
+        <v>0.2184517780033636</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3736066150410062</v>
+        <v>0.3678588209634522</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.232757042784673</v>
+        <v>0.234657042784673</v>
       </c>
       <c r="C67">
-        <v>-4.825959251809767</v>
+        <v>-5.504431953457615</v>
       </c>
       <c r="D67">
-        <v>16.97454074819024</v>
+        <v>16.80376804654239</v>
       </c>
       <c r="E67">
-        <v>26.4305</v>
+        <v>26.9382</v>
       </c>
       <c r="F67">
-        <v>33.0005</v>
+        <v>33.5082</v>
       </c>
       <c r="G67">
         <v>11.2</v>
@@ -6915,37 +6915,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M67">
-        <v>7.781517900000001</v>
+        <v>7.901233560000001</v>
       </c>
       <c r="N67">
-        <v>-4.919017900000002</v>
+        <v>-5.038733560000001</v>
       </c>
       <c r="O67">
-        <v>-0.9838035800000005</v>
+        <v>-1.007746712</v>
       </c>
       <c r="P67">
-        <v>-3.935214320000001</v>
+        <v>-4.030986848</v>
       </c>
       <c r="Q67">
-        <v>-2.785214320000001</v>
+        <v>-2.880986848</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2593239630928189</v>
+        <v>0.2656040796543724</v>
       </c>
       <c r="T67">
-        <v>2.338174914198427</v>
+        <v>2.406944764616028</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07357176419269046</v>
+        <v>0.0724570404928012</v>
       </c>
       <c r="W67">
-        <v>0.2184517780033636</v>
+        <v>0.2187146298517975</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3678588209634522</v>
+        <v>0.3622852024640061</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.234657042784673</v>
+        <v>0.236557042784673</v>
       </c>
       <c r="C68">
-        <v>-5.504431953457615</v>
+        <v>-6.179502755721884</v>
       </c>
       <c r="D68">
-        <v>16.80376804654239</v>
+        <v>16.63639724427812</v>
       </c>
       <c r="E68">
-        <v>26.9382</v>
+        <v>27.4459</v>
       </c>
       <c r="F68">
-        <v>33.5082</v>
+        <v>34.0159</v>
       </c>
       <c r="G68">
         <v>11.2</v>
@@ -6997,37 +6997,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M68">
-        <v>7.901233560000001</v>
+        <v>8.02094922</v>
       </c>
       <c r="N68">
-        <v>-5.038733560000001</v>
+        <v>-5.158449220000001</v>
       </c>
       <c r="O68">
-        <v>-1.007746712</v>
+        <v>-1.031689844</v>
       </c>
       <c r="P68">
-        <v>-4.030986848</v>
+        <v>-4.126759376000001</v>
       </c>
       <c r="Q68">
-        <v>-2.880986848</v>
+        <v>-2.976759376000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2656040796543724</v>
+        <v>0.2722648093408686</v>
       </c>
       <c r="T68">
-        <v>2.406944764616028</v>
+        <v>2.479882484755908</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0724570404928012</v>
+        <v>0.07137559212723701</v>
       </c>
       <c r="W68">
-        <v>0.2187146298517975</v>
+        <v>0.2189696353763975</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3622852024640061</v>
+        <v>0.356877960636185</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.236557042784673</v>
+        <v>0.238457042784673</v>
       </c>
       <c r="C69">
-        <v>-6.179502755721884</v>
+        <v>-6.851272308058245</v>
       </c>
       <c r="D69">
-        <v>16.63639724427812</v>
+        <v>16.47232769194176</v>
       </c>
       <c r="E69">
-        <v>27.4459</v>
+        <v>27.9536</v>
       </c>
       <c r="F69">
-        <v>34.0159</v>
+        <v>34.5236</v>
       </c>
       <c r="G69">
         <v>11.2</v>
@@ -7079,37 +7079,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M69">
-        <v>8.02094922</v>
+        <v>8.140664880000001</v>
       </c>
       <c r="N69">
-        <v>-5.158449220000001</v>
+        <v>-5.278164880000002</v>
       </c>
       <c r="O69">
-        <v>-1.031689844</v>
+        <v>-1.055632976000001</v>
       </c>
       <c r="P69">
-        <v>-4.126759376000001</v>
+        <v>-4.222531904000002</v>
       </c>
       <c r="Q69">
-        <v>-2.976759376000001</v>
+        <v>-3.072531904000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2722648093408686</v>
+        <v>0.2793418346327707</v>
       </c>
       <c r="T69">
-        <v>2.479882484755908</v>
+        <v>2.55737881240453</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07137559212723701</v>
+        <v>0.07032595106654235</v>
       </c>
       <c r="W69">
-        <v>0.2189696353763975</v>
+        <v>0.2192171407385093</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.356877960636185</v>
+        <v>0.3516297553327117</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.238457042784673</v>
+        <v>0.240357042784673</v>
       </c>
       <c r="C70">
-        <v>-6.851272308058245</v>
+        <v>-7.519837328243241</v>
       </c>
       <c r="D70">
-        <v>16.47232769194176</v>
+        <v>16.31146267175676</v>
       </c>
       <c r="E70">
-        <v>27.9536</v>
+        <v>28.4613</v>
       </c>
       <c r="F70">
-        <v>34.5236</v>
+        <v>35.0313</v>
       </c>
       <c r="G70">
         <v>11.2</v>
@@ -7161,37 +7161,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M70">
-        <v>8.140664880000001</v>
+        <v>8.26038054</v>
       </c>
       <c r="N70">
-        <v>-5.278164880000002</v>
+        <v>-5.397880540000001</v>
       </c>
       <c r="O70">
-        <v>-1.055632976000001</v>
+        <v>-1.079576108</v>
       </c>
       <c r="P70">
-        <v>-4.222531904000002</v>
+        <v>-4.318304432000001</v>
       </c>
       <c r="Q70">
-        <v>-3.072531904000002</v>
+        <v>-3.168304432000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2793418346327707</v>
+        <v>0.2868754422015698</v>
       </c>
       <c r="T70">
-        <v>2.55737881240453</v>
+        <v>2.639874903127257</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07032595106654235</v>
+        <v>0.06930673438441856</v>
       </c>
       <c r="W70">
-        <v>0.2192171407385093</v>
+        <v>0.2194574720321541</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3516297553327117</v>
+        <v>0.3465336719220927</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.240357042784673</v>
+        <v>0.242257042784673</v>
       </c>
       <c r="C71">
-        <v>-7.519837328243241</v>
+        <v>-8.185290792497042</v>
       </c>
       <c r="D71">
-        <v>16.31146267175676</v>
+        <v>16.15370920750297</v>
       </c>
       <c r="E71">
-        <v>28.4613</v>
+        <v>28.96900000000001</v>
       </c>
       <c r="F71">
-        <v>35.0313</v>
+        <v>35.53900000000001</v>
       </c>
       <c r="G71">
         <v>11.2</v>
@@ -7243,37 +7243,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M71">
-        <v>8.26038054</v>
+        <v>8.380096200000002</v>
       </c>
       <c r="N71">
-        <v>-5.397880540000001</v>
+        <v>-5.517596200000003</v>
       </c>
       <c r="O71">
-        <v>-1.079576108</v>
+        <v>-1.103519240000001</v>
       </c>
       <c r="P71">
-        <v>-4.318304432000001</v>
+        <v>-4.414076960000003</v>
       </c>
       <c r="Q71">
-        <v>-3.168304432000001</v>
+        <v>-3.264076960000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2868754422015698</v>
+        <v>0.2949112902749554</v>
       </c>
       <c r="T71">
-        <v>2.639874903127257</v>
+        <v>2.727870733231499</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06930673438441856</v>
+        <v>0.06831663817892684</v>
       </c>
       <c r="W71">
-        <v>0.2194574720321541</v>
+        <v>0.2196909367174091</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3465336719220927</v>
+        <v>0.3415831908946342</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.242257042784673</v>
+        <v>0.244157042784673</v>
       </c>
       <c r="C72">
-        <v>-8.185290792497042</v>
+        <v>-8.847722114679399</v>
       </c>
       <c r="D72">
-        <v>16.15370920750297</v>
+        <v>15.99897788532061</v>
       </c>
       <c r="E72">
-        <v>28.96900000000001</v>
+        <v>29.47670000000001</v>
       </c>
       <c r="F72">
-        <v>35.53900000000001</v>
+        <v>36.04670000000001</v>
       </c>
       <c r="G72">
         <v>11.2</v>
@@ -7325,37 +7325,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M72">
-        <v>8.380096200000002</v>
+        <v>8.499811860000003</v>
       </c>
       <c r="N72">
-        <v>-5.517596200000003</v>
+        <v>-5.637311860000004</v>
       </c>
       <c r="O72">
-        <v>-1.103519240000001</v>
+        <v>-1.127462372000001</v>
       </c>
       <c r="P72">
-        <v>-4.414076960000003</v>
+        <v>-4.509849488000003</v>
       </c>
       <c r="Q72">
-        <v>-3.264076960000003</v>
+        <v>-3.359849488000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2949112902749554</v>
+        <v>0.3035013347671953</v>
       </c>
       <c r="T72">
-        <v>2.727870733231499</v>
+        <v>2.821935241273964</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06831663817892684</v>
+        <v>0.06735443200739265</v>
       </c>
       <c r="W72">
-        <v>0.2196909367174091</v>
+        <v>0.2199178249326568</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3415831908946342</v>
+        <v>0.3367721600369632</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.244157042784673</v>
+        <v>0.2460570427846729</v>
       </c>
       <c r="C73">
-        <v>-8.847722114679392</v>
+        <v>-9.50721731528462</v>
       </c>
       <c r="D73">
-        <v>15.99897788532061</v>
+        <v>15.84718268471538</v>
       </c>
       <c r="E73">
-        <v>29.4767</v>
+        <v>29.9844</v>
       </c>
       <c r="F73">
-        <v>36.0467</v>
+        <v>36.5544</v>
       </c>
       <c r="G73">
         <v>11.2</v>
@@ -7407,37 +7407,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M73">
-        <v>8.499811860000001</v>
+        <v>8.61952752</v>
       </c>
       <c r="N73">
-        <v>-5.637311860000002</v>
+        <v>-5.757027520000001</v>
       </c>
       <c r="O73">
-        <v>-1.127462372000001</v>
+        <v>-1.151405504</v>
       </c>
       <c r="P73">
-        <v>-4.509849488000002</v>
+        <v>-4.605622016000001</v>
       </c>
       <c r="Q73">
-        <v>-3.359849488000002</v>
+        <v>-3.455622016000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3035013347671953</v>
+        <v>0.3127049538660236</v>
       </c>
       <c r="T73">
-        <v>2.821935241273964</v>
+        <v>2.922718642748034</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06735443200739266</v>
+        <v>0.06641895378506778</v>
       </c>
       <c r="W73">
-        <v>0.2199178249326568</v>
+        <v>0.220138410697481</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3367721600369633</v>
+        <v>0.3320947689253388</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2460570427846729</v>
+        <v>0.247957042784673</v>
       </c>
       <c r="C74">
-        <v>-9.50721731528462</v>
+        <v>-10.16385918090654</v>
       </c>
       <c r="D74">
-        <v>15.84718268471538</v>
+        <v>15.69824081909346</v>
       </c>
       <c r="E74">
-        <v>29.9844</v>
+        <v>30.4921</v>
       </c>
       <c r="F74">
-        <v>36.5544</v>
+        <v>37.0621</v>
       </c>
       <c r="G74">
         <v>11.2</v>
@@ -7489,37 +7489,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M74">
-        <v>8.61952752</v>
+        <v>8.739243180000001</v>
       </c>
       <c r="N74">
-        <v>-5.757027520000001</v>
+        <v>-5.876743180000002</v>
       </c>
       <c r="O74">
-        <v>-1.151405504</v>
+        <v>-1.175348636000001</v>
       </c>
       <c r="P74">
-        <v>-4.605622016000001</v>
+        <v>-4.701394544000001</v>
       </c>
       <c r="Q74">
-        <v>-3.455622016000001</v>
+        <v>-3.551394544000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3127049538660236</v>
+        <v>0.3225903225277282</v>
       </c>
       <c r="T74">
-        <v>2.922718642748034</v>
+        <v>3.030967481368331</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06641895378506778</v>
+        <v>0.06550910510308054</v>
       </c>
       <c r="W74">
-        <v>0.220138410697481</v>
+        <v>0.2203529530166936</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3320947689253388</v>
+        <v>0.3275455255154026</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.247957042784673</v>
+        <v>0.249857042784673</v>
       </c>
       <c r="C75">
-        <v>-10.16385918090654</v>
+        <v>-10.81772741479471</v>
       </c>
       <c r="D75">
-        <v>15.69824081909346</v>
+        <v>15.55207258520529</v>
       </c>
       <c r="E75">
-        <v>30.4921</v>
+        <v>30.9998</v>
       </c>
       <c r="F75">
-        <v>37.0621</v>
+        <v>37.5698</v>
       </c>
       <c r="G75">
         <v>11.2</v>
@@ -7571,37 +7571,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M75">
-        <v>8.739243180000001</v>
+        <v>8.85895884</v>
       </c>
       <c r="N75">
-        <v>-5.876743180000002</v>
+        <v>-5.996458840000001</v>
       </c>
       <c r="O75">
-        <v>-1.175348636000001</v>
+        <v>-1.199291768</v>
       </c>
       <c r="P75">
-        <v>-4.701394544000001</v>
+        <v>-4.797167072000001</v>
       </c>
       <c r="Q75">
-        <v>-3.551394544000001</v>
+        <v>-3.647167072000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3225903225277282</v>
+        <v>0.3332361041634101</v>
       </c>
       <c r="T75">
-        <v>3.030967481368331</v>
+        <v>3.147543153728652</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06550910510308054</v>
+        <v>0.0646238469260119</v>
       </c>
       <c r="W75">
-        <v>0.2203529530166936</v>
+        <v>0.2205616968948464</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3275455255154026</v>
+        <v>0.3231192346300594</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.249857042784673</v>
+        <v>0.251757042784673</v>
       </c>
       <c r="C76">
-        <v>-10.81772741479471</v>
+        <v>-11.46889877907713</v>
       </c>
       <c r="D76">
-        <v>15.55207258520529</v>
+        <v>15.40860122092287</v>
       </c>
       <c r="E76">
-        <v>30.9998</v>
+        <v>31.5075</v>
       </c>
       <c r="F76">
-        <v>37.5698</v>
+        <v>38.0775</v>
       </c>
       <c r="G76">
         <v>11.2</v>
@@ -7653,37 +7653,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M76">
-        <v>8.85895884</v>
+        <v>8.9786745</v>
       </c>
       <c r="N76">
-        <v>-5.996458840000001</v>
+        <v>-6.116174500000001</v>
       </c>
       <c r="O76">
-        <v>-1.199291768</v>
+        <v>-1.2232349</v>
       </c>
       <c r="P76">
-        <v>-4.797167072000001</v>
+        <v>-4.892939600000001</v>
       </c>
       <c r="Q76">
-        <v>-3.647167072000001</v>
+        <v>-3.742939600000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3332361041634101</v>
+        <v>0.3447335483299465</v>
       </c>
       <c r="T76">
-        <v>3.147543153728652</v>
+        <v>3.273444879877798</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.0646238469260119</v>
+        <v>0.06376219563366507</v>
       </c>
       <c r="W76">
-        <v>0.2205616968948464</v>
+        <v>0.2207648742695818</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3231192346300594</v>
+        <v>0.3188109781683253</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.251757042784673</v>
+        <v>0.2536570427846729</v>
       </c>
       <c r="C77">
-        <v>-11.46889877907713</v>
+        <v>-12.11744722918272</v>
       </c>
       <c r="D77">
-        <v>15.40860122092287</v>
+        <v>15.26775277081728</v>
       </c>
       <c r="E77">
-        <v>31.5075</v>
+        <v>32.0152</v>
       </c>
       <c r="F77">
-        <v>38.0775</v>
+        <v>38.5852</v>
       </c>
       <c r="G77">
         <v>11.2</v>
@@ -7735,37 +7735,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M77">
-        <v>8.9786745</v>
+        <v>9.098390160000001</v>
       </c>
       <c r="N77">
-        <v>-6.116174500000001</v>
+        <v>-6.235890160000002</v>
       </c>
       <c r="O77">
-        <v>-1.2232349</v>
+        <v>-1.247178032000001</v>
       </c>
       <c r="P77">
-        <v>-4.892939600000001</v>
+        <v>-4.988712128000001</v>
       </c>
       <c r="Q77">
-        <v>-3.742939600000001</v>
+        <v>-3.838712128000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3447335483299465</v>
+        <v>0.3571891128436943</v>
       </c>
       <c r="T77">
-        <v>3.273444879877798</v>
+        <v>3.409838416539372</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06376219563366507</v>
+        <v>0.06292321937532737</v>
       </c>
       <c r="W77">
-        <v>0.2207648742695818</v>
+        <v>0.2209627048712978</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3188109781683253</v>
+        <v>0.3146160968766367</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2536570427846729</v>
+        <v>0.2555570427846729</v>
       </c>
       <c r="C78">
-        <v>-12.11744722918272</v>
+        <v>-12.7634440409581</v>
       </c>
       <c r="D78">
-        <v>15.26775277081728</v>
+        <v>15.1294559590419</v>
       </c>
       <c r="E78">
-        <v>32.0152</v>
+        <v>32.5229</v>
       </c>
       <c r="F78">
-        <v>38.5852</v>
+        <v>39.0929</v>
       </c>
       <c r="G78">
         <v>11.2</v>
@@ -7817,37 +7817,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M78">
-        <v>9.098390160000001</v>
+        <v>9.21810582</v>
       </c>
       <c r="N78">
-        <v>-6.235890160000002</v>
+        <v>-6.355605820000001</v>
       </c>
       <c r="O78">
-        <v>-1.247178032000001</v>
+        <v>-1.271121164</v>
       </c>
       <c r="P78">
-        <v>-4.988712128000001</v>
+        <v>-5.084484656000001</v>
       </c>
       <c r="Q78">
-        <v>-3.838712128000001</v>
+        <v>-3.934484656000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3571891128436943</v>
+        <v>0.3707277699238549</v>
       </c>
       <c r="T78">
-        <v>3.409838416539372</v>
+        <v>3.558092260736736</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06292321937532737</v>
+        <v>0.06210603470811532</v>
       </c>
       <c r="W78">
-        <v>0.2209627048712978</v>
+        <v>0.2211553970158264</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3146160968766367</v>
+        <v>0.3105301735405765</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2555570427846729</v>
+        <v>0.257457042784673</v>
       </c>
       <c r="C79">
-        <v>-12.7634440409581</v>
+        <v>-13.40695793093778</v>
       </c>
       <c r="D79">
-        <v>15.1294559590419</v>
+        <v>14.99364206906223</v>
       </c>
       <c r="E79">
-        <v>32.5229</v>
+        <v>33.03060000000001</v>
       </c>
       <c r="F79">
-        <v>39.0929</v>
+        <v>39.60060000000001</v>
       </c>
       <c r="G79">
         <v>11.2</v>
@@ -7899,37 +7899,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M79">
-        <v>9.21810582</v>
+        <v>9.337821480000002</v>
       </c>
       <c r="N79">
-        <v>-6.355605820000001</v>
+        <v>-6.475321480000003</v>
       </c>
       <c r="O79">
-        <v>-1.271121164</v>
+        <v>-1.295064296000001</v>
       </c>
       <c r="P79">
-        <v>-5.084484656000001</v>
+        <v>-5.180257184000003</v>
       </c>
       <c r="Q79">
-        <v>-3.934484656000001</v>
+        <v>-4.030257184000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3707277699238549</v>
+        <v>0.3854972140113029</v>
       </c>
       <c r="T79">
-        <v>3.558092260736736</v>
+        <v>3.719823727133862</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06210603470811532</v>
+        <v>0.0613098034939087</v>
       </c>
       <c r="W79">
-        <v>0.2211553970158264</v>
+        <v>0.2213431483361363</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3105301735405765</v>
+        <v>0.3065490174695434</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.257457042784673</v>
+        <v>0.259357042784673</v>
       </c>
       <c r="C80">
-        <v>-13.40695793093778</v>
+        <v>-14.0480551701941</v>
       </c>
       <c r="D80">
-        <v>14.99364206906223</v>
+        <v>14.86024482980591</v>
       </c>
       <c r="E80">
-        <v>33.03060000000001</v>
+        <v>33.53830000000001</v>
       </c>
       <c r="F80">
-        <v>39.60060000000001</v>
+        <v>40.10830000000001</v>
       </c>
       <c r="G80">
         <v>11.2</v>
@@ -7981,37 +7981,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M80">
-        <v>9.337821480000002</v>
+        <v>9.457537140000001</v>
       </c>
       <c r="N80">
-        <v>-6.475321480000003</v>
+        <v>-6.595037140000002</v>
       </c>
       <c r="O80">
-        <v>-1.295064296000001</v>
+        <v>-1.319007428000001</v>
       </c>
       <c r="P80">
-        <v>-5.180257184000003</v>
+        <v>-5.276029712000001</v>
       </c>
       <c r="Q80">
-        <v>-4.030257184000003</v>
+        <v>-4.126029712000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3854972140113029</v>
+        <v>0.401673271821365</v>
       </c>
       <c r="T80">
-        <v>3.719823727133862</v>
+        <v>3.896958190330713</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.0613098034939087</v>
+        <v>0.0605337300319605</v>
       </c>
       <c r="W80">
-        <v>0.2213431483361363</v>
+        <v>0.2215261464584637</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3065490174695434</v>
+        <v>0.3026686501598025</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.259357042784673</v>
+        <v>0.261257042784673</v>
       </c>
       <c r="C81">
-        <v>-14.0480551701941</v>
+        <v>-14.68679969216337</v>
       </c>
       <c r="D81">
-        <v>14.86024482980591</v>
+        <v>14.72920030783663</v>
       </c>
       <c r="E81">
-        <v>33.53830000000001</v>
+        <v>34.04600000000001</v>
       </c>
       <c r="F81">
-        <v>40.10830000000001</v>
+        <v>40.61600000000001</v>
       </c>
       <c r="G81">
         <v>11.2</v>
@@ -8063,37 +8063,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M81">
-        <v>9.457537140000001</v>
+        <v>9.577252800000002</v>
       </c>
       <c r="N81">
-        <v>-6.595037140000002</v>
+        <v>-6.714752800000003</v>
       </c>
       <c r="O81">
-        <v>-1.319007428000001</v>
+        <v>-1.342950560000001</v>
       </c>
       <c r="P81">
-        <v>-5.276029712000001</v>
+        <v>-5.371802240000003</v>
       </c>
       <c r="Q81">
-        <v>-4.126029712000001</v>
+        <v>-4.221802240000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.401673271821365</v>
+        <v>0.4194669354124332</v>
       </c>
       <c r="T81">
-        <v>3.896958190330713</v>
+        <v>4.091806099847248</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0605337300319605</v>
+        <v>0.05977705840656099</v>
       </c>
       <c r="W81">
-        <v>0.2215261464584637</v>
+        <v>0.2217045696277329</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3026686501598025</v>
+        <v>0.2988852920328049</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.261257042784673</v>
+        <v>0.2631570427846729</v>
       </c>
       <c r="C82">
-        <v>-14.68679969216337</v>
+        <v>-15.32325319481667</v>
       </c>
       <c r="D82">
-        <v>14.72920030783663</v>
+        <v>14.60044680518334</v>
       </c>
       <c r="E82">
-        <v>34.04600000000001</v>
+        <v>34.55370000000001</v>
       </c>
       <c r="F82">
-        <v>40.61600000000001</v>
+        <v>41.12370000000001</v>
       </c>
       <c r="G82">
         <v>11.2</v>
@@ -8145,37 +8145,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M82">
-        <v>9.577252800000002</v>
+        <v>9.696968460000003</v>
       </c>
       <c r="N82">
-        <v>-6.714752800000003</v>
+        <v>-6.834468460000004</v>
       </c>
       <c r="O82">
-        <v>-1.342950560000001</v>
+        <v>-1.366893692000001</v>
       </c>
       <c r="P82">
-        <v>-5.371802240000003</v>
+        <v>-5.467574768000003</v>
       </c>
       <c r="Q82">
-        <v>-4.221802240000002</v>
+        <v>-4.317574768000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4194669354124332</v>
+        <v>0.4391336162236139</v>
       </c>
       <c r="T82">
-        <v>4.091806099847248</v>
+        <v>4.307164315628683</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05977705840656099</v>
+        <v>0.05903907003117135</v>
       </c>
       <c r="W82">
-        <v>0.2217045696277329</v>
+        <v>0.2218785872866498</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2988852920328049</v>
+        <v>0.2951953501558566</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2631570427846729</v>
+        <v>0.265057042784673</v>
       </c>
       <c r="C83">
-        <v>-15.32325319481667</v>
+        <v>-15.95747523751836</v>
       </c>
       <c r="D83">
-        <v>14.60044680518334</v>
+        <v>14.47392476248165</v>
       </c>
       <c r="E83">
-        <v>34.55370000000001</v>
+        <v>35.06140000000001</v>
       </c>
       <c r="F83">
-        <v>41.12370000000001</v>
+        <v>41.63140000000001</v>
       </c>
       <c r="G83">
         <v>11.2</v>
@@ -8227,37 +8227,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M83">
-        <v>9.696968460000003</v>
+        <v>9.816684120000001</v>
       </c>
       <c r="N83">
-        <v>-6.834468460000004</v>
+        <v>-6.954184120000003</v>
       </c>
       <c r="O83">
-        <v>-1.366893692000001</v>
+        <v>-1.390836824000001</v>
       </c>
       <c r="P83">
-        <v>-5.467574768000003</v>
+        <v>-5.563347296000002</v>
       </c>
       <c r="Q83">
-        <v>-4.317574768000004</v>
+        <v>-4.413347296000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4391336162236139</v>
+        <v>0.4609854837915925</v>
       </c>
       <c r="T83">
-        <v>4.307164315628683</v>
+        <v>4.546451222052498</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05903907003117135</v>
+        <v>0.05831908137225462</v>
       </c>
       <c r="W83">
-        <v>0.2218785872866498</v>
+        <v>0.2220483606124224</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2951953501558566</v>
+        <v>0.2915954068612731</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.265057042784673</v>
+        <v>0.266957042784673</v>
       </c>
       <c r="C84">
-        <v>-15.95747523751836</v>
+        <v>-16.58952333289189</v>
       </c>
       <c r="D84">
-        <v>14.47392476248165</v>
+        <v>14.34957666710812</v>
       </c>
       <c r="E84">
-        <v>35.06140000000001</v>
+        <v>35.56910000000001</v>
       </c>
       <c r="F84">
-        <v>41.63140000000001</v>
+        <v>42.13910000000001</v>
       </c>
       <c r="G84">
         <v>11.2</v>
@@ -8309,37 +8309,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M84">
-        <v>9.816684120000001</v>
+        <v>9.936399780000002</v>
       </c>
       <c r="N84">
-        <v>-6.954184120000003</v>
+        <v>-7.073899780000003</v>
       </c>
       <c r="O84">
-        <v>-1.390836824000001</v>
+        <v>-1.414779956000001</v>
       </c>
       <c r="P84">
-        <v>-5.563347296000002</v>
+        <v>-5.659119824000003</v>
       </c>
       <c r="Q84">
-        <v>-4.413347296000001</v>
+        <v>-4.509119824000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4609854837915925</v>
+        <v>0.485408159308745</v>
       </c>
       <c r="T84">
-        <v>4.546451222052498</v>
+        <v>4.813889529232058</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05831908137225462</v>
+        <v>0.05761644183764915</v>
       </c>
       <c r="W84">
-        <v>0.2220483606124224</v>
+        <v>0.2222140430146823</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2915954068612731</v>
+        <v>0.2880822091882457</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.266957042784673</v>
+        <v>0.268857042784673</v>
       </c>
       <c r="C85">
-        <v>-16.58952333289189</v>
+        <v>-17.21945303399047</v>
       </c>
       <c r="D85">
-        <v>14.34957666710812</v>
+        <v>14.22734696600954</v>
       </c>
       <c r="E85">
-        <v>35.56910000000001</v>
+        <v>36.07680000000001</v>
       </c>
       <c r="F85">
-        <v>42.13910000000001</v>
+        <v>42.64680000000001</v>
       </c>
       <c r="G85">
         <v>11.2</v>
@@ -8391,37 +8391,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M85">
-        <v>9.936399780000002</v>
+        <v>10.05611544</v>
       </c>
       <c r="N85">
-        <v>-7.073899780000003</v>
+        <v>-7.193615440000002</v>
       </c>
       <c r="O85">
-        <v>-1.414779956000001</v>
+        <v>-1.438723088000001</v>
       </c>
       <c r="P85">
-        <v>-5.659119824000003</v>
+        <v>-5.754892352000001</v>
       </c>
       <c r="Q85">
-        <v>-4.509119824000003</v>
+        <v>-4.604892352000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.485408159308745</v>
+        <v>0.5128836692655416</v>
       </c>
       <c r="T85">
-        <v>4.813889529232058</v>
+        <v>5.114757624809062</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05761644183764915</v>
+        <v>0.05693053181577238</v>
       </c>
       <c r="W85">
-        <v>0.2222140430146823</v>
+        <v>0.2223757805978409</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2880822091882457</v>
+        <v>0.2846526590788618</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.268857042784673</v>
+        <v>0.2707570427846729</v>
       </c>
       <c r="C86">
-        <v>-17.21945303399046</v>
+        <v>-17.84731801705033</v>
       </c>
       <c r="D86">
-        <v>14.22734696600954</v>
+        <v>14.10718198294967</v>
       </c>
       <c r="E86">
-        <v>36.0768</v>
+        <v>36.5845</v>
       </c>
       <c r="F86">
-        <v>42.6468</v>
+        <v>43.1545</v>
       </c>
       <c r="G86">
         <v>11.2</v>
@@ -8473,37 +8473,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M86">
-        <v>10.05611544</v>
+        <v>10.1758311</v>
       </c>
       <c r="N86">
-        <v>-7.193615440000002</v>
+        <v>-7.313331100000001</v>
       </c>
       <c r="O86">
-        <v>-1.438723088000001</v>
+        <v>-1.46266622</v>
       </c>
       <c r="P86">
-        <v>-5.754892352000001</v>
+        <v>-5.850664880000001</v>
       </c>
       <c r="Q86">
-        <v>-4.604892352000002</v>
+        <v>-4.700664880000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5128836692655413</v>
+        <v>0.5440225805499107</v>
       </c>
       <c r="T86">
-        <v>5.114757624809059</v>
+        <v>5.455741466462996</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05693053181577238</v>
+        <v>0.05626076085323389</v>
       </c>
       <c r="W86">
-        <v>0.2223757805978409</v>
+        <v>0.2225337125908075</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2846526590788618</v>
+        <v>0.2813038042661694</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2707570427846729</v>
+        <v>0.272657042784673</v>
       </c>
       <c r="C87">
-        <v>-17.84731801705033</v>
+        <v>-18.47317016008538</v>
       </c>
       <c r="D87">
-        <v>14.10718198294967</v>
+        <v>13.98902983991462</v>
       </c>
       <c r="E87">
-        <v>36.5845</v>
+        <v>37.0922</v>
       </c>
       <c r="F87">
-        <v>43.1545</v>
+        <v>43.6622</v>
       </c>
       <c r="G87">
         <v>11.2</v>
@@ -8555,37 +8555,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M87">
-        <v>10.1758311</v>
+        <v>10.29554676</v>
       </c>
       <c r="N87">
-        <v>-7.313331100000001</v>
+        <v>-7.433046760000002</v>
       </c>
       <c r="O87">
-        <v>-1.46266622</v>
+        <v>-1.486609352</v>
       </c>
       <c r="P87">
-        <v>-5.850664880000001</v>
+        <v>-5.946437408000001</v>
       </c>
       <c r="Q87">
-        <v>-4.700664880000001</v>
+        <v>-4.796437408000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5440225805499107</v>
+        <v>0.5796099077320472</v>
       </c>
       <c r="T87">
-        <v>5.455741466462996</v>
+        <v>5.845437285496067</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05626076085323389</v>
+        <v>0.05560656595959163</v>
       </c>
       <c r="W87">
-        <v>0.2225337125908075</v>
+        <v>0.2226879717467283</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2813038042661694</v>
+        <v>0.2780328297979581</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.272657042784673</v>
+        <v>0.274557042784673</v>
       </c>
       <c r="C88">
-        <v>-18.47317016008538</v>
+        <v>-19.09705961756521</v>
       </c>
       <c r="D88">
-        <v>13.98902983991462</v>
+        <v>13.8728403824348</v>
       </c>
       <c r="E88">
-        <v>37.0922</v>
+        <v>37.59990000000001</v>
       </c>
       <c r="F88">
-        <v>43.6622</v>
+        <v>44.16990000000001</v>
       </c>
       <c r="G88">
         <v>11.2</v>
@@ -8637,37 +8637,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M88">
-        <v>10.29554676</v>
+        <v>10.41526242</v>
       </c>
       <c r="N88">
-        <v>-7.433046760000002</v>
+        <v>-7.552762420000002</v>
       </c>
       <c r="O88">
-        <v>-1.486609352</v>
+        <v>-1.510552484000001</v>
       </c>
       <c r="P88">
-        <v>-5.946437408000001</v>
+        <v>-6.042209936000002</v>
       </c>
       <c r="Q88">
-        <v>-4.796437408000001</v>
+        <v>-4.892209936000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5796099077320472</v>
+        <v>0.6206722083268201</v>
       </c>
       <c r="T88">
-        <v>5.845437285496067</v>
+        <v>6.295086307457304</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05560656595959163</v>
+        <v>0.05496741002902161</v>
       </c>
       <c r="W88">
-        <v>0.2226879717467283</v>
+        <v>0.2228386847151567</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2780328297979581</v>
+        <v>0.274837050145108</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.274557042784673</v>
+        <v>0.276457042784673</v>
       </c>
       <c r="C89">
-        <v>-19.09705961756521</v>
+        <v>-19.7190348914021</v>
       </c>
       <c r="D89">
-        <v>13.8728403824348</v>
+        <v>13.75856510859791</v>
       </c>
       <c r="E89">
-        <v>37.59990000000001</v>
+        <v>38.10760000000001</v>
       </c>
       <c r="F89">
-        <v>44.16990000000001</v>
+        <v>44.67760000000001</v>
       </c>
       <c r="G89">
         <v>11.2</v>
@@ -8719,37 +8719,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M89">
-        <v>10.41526242</v>
+        <v>10.53497808</v>
       </c>
       <c r="N89">
-        <v>-7.552762420000002</v>
+        <v>-7.672478080000003</v>
       </c>
       <c r="O89">
-        <v>-1.510552484000001</v>
+        <v>-1.534495616000001</v>
       </c>
       <c r="P89">
-        <v>-6.042209936000002</v>
+        <v>-6.137982464000002</v>
       </c>
       <c r="Q89">
-        <v>-4.892209936000002</v>
+        <v>-4.987982464000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6206722083268201</v>
+        <v>0.6685782256873884</v>
       </c>
       <c r="T89">
-        <v>6.295086307457304</v>
+        <v>6.819676833078746</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05496741002902161</v>
+        <v>0.0543427803696009</v>
       </c>
       <c r="W89">
-        <v>0.2228386847151567</v>
+        <v>0.2229859723888481</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.274837050145108</v>
+        <v>0.2717139018480045</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.276457042784673</v>
+        <v>0.2783570427846729</v>
       </c>
       <c r="C90">
-        <v>-19.7190348914021</v>
+        <v>-20.33914289845842</v>
       </c>
       <c r="D90">
-        <v>13.75856510859791</v>
+        <v>13.64615710154159</v>
       </c>
       <c r="E90">
-        <v>38.10760000000001</v>
+        <v>38.6153</v>
       </c>
       <c r="F90">
-        <v>44.67760000000001</v>
+        <v>45.18530000000001</v>
       </c>
       <c r="G90">
         <v>11.2</v>
@@ -8801,37 +8801,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M90">
-        <v>10.53497808</v>
+        <v>10.65469374</v>
       </c>
       <c r="N90">
-        <v>-7.672478080000003</v>
+        <v>-7.792193740000002</v>
       </c>
       <c r="O90">
-        <v>-1.534495616000001</v>
+        <v>-1.558438748</v>
       </c>
       <c r="P90">
-        <v>-6.137982464000002</v>
+        <v>-6.233754992000001</v>
       </c>
       <c r="Q90">
-        <v>-4.987982464000002</v>
+        <v>-5.083754992000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6685782256873884</v>
+        <v>0.7251944280226057</v>
       </c>
       <c r="T90">
-        <v>6.819676833078746</v>
+        <v>7.439647454267724</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0543427803696009</v>
+        <v>0.05373218733174023</v>
       </c>
       <c r="W90">
-        <v>0.2229859723888481</v>
+        <v>0.2231299502271757</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2717139018480045</v>
+        <v>0.2686609366587011</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2783570427846729</v>
+        <v>0.2802570427846729</v>
       </c>
       <c r="C91">
-        <v>-20.33914289845842</v>
+        <v>-20.95742903477142</v>
       </c>
       <c r="D91">
-        <v>13.64615710154159</v>
+        <v>13.53557096522859</v>
       </c>
       <c r="E91">
-        <v>38.6153</v>
+        <v>39.123</v>
       </c>
       <c r="F91">
-        <v>45.18530000000001</v>
+        <v>45.693</v>
       </c>
       <c r="G91">
         <v>11.2</v>
@@ -8883,37 +8883,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M91">
-        <v>10.65469374</v>
+        <v>10.7744094</v>
       </c>
       <c r="N91">
-        <v>-7.792193740000002</v>
+        <v>-7.911909400000003</v>
       </c>
       <c r="O91">
-        <v>-1.558438748</v>
+        <v>-1.582381880000001</v>
       </c>
       <c r="P91">
-        <v>-6.233754992000001</v>
+        <v>-6.329527520000002</v>
       </c>
       <c r="Q91">
-        <v>-5.083754992000001</v>
+        <v>-5.179527520000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7251944280226057</v>
+        <v>0.7931338708248664</v>
       </c>
       <c r="T91">
-        <v>7.439647454267724</v>
+        <v>8.183612199694497</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05373218733174023</v>
+        <v>0.05313516302805421</v>
       </c>
       <c r="W91">
-        <v>0.2231299502271757</v>
+        <v>0.2232707285579848</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2686609366587011</v>
+        <v>0.2656758151402711</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2802570427846729</v>
+        <v>0.282157042784673</v>
       </c>
       <c r="C92">
-        <v>-20.95742903477142</v>
+        <v>-21.57393723668044</v>
       </c>
       <c r="D92">
-        <v>13.53557096522859</v>
+        <v>13.42676276331957</v>
       </c>
       <c r="E92">
-        <v>39.123</v>
+        <v>39.6307</v>
       </c>
       <c r="F92">
-        <v>45.693</v>
+        <v>46.2007</v>
       </c>
       <c r="G92">
         <v>11.2</v>
@@ -8965,37 +8965,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M92">
-        <v>10.7744094</v>
+        <v>10.89412506</v>
       </c>
       <c r="N92">
-        <v>-7.911909400000003</v>
+        <v>-8.031625060000003</v>
       </c>
       <c r="O92">
-        <v>-1.582381880000001</v>
+        <v>-1.606325012000001</v>
       </c>
       <c r="P92">
-        <v>-6.329527520000002</v>
+        <v>-6.425300048000002</v>
       </c>
       <c r="Q92">
-        <v>-5.179527520000002</v>
+        <v>-5.275300048000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7931338708248664</v>
+        <v>0.8761709675831849</v>
       </c>
       <c r="T92">
-        <v>8.183612199694497</v>
+        <v>9.092902444104997</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05313516302805421</v>
+        <v>0.05255126013763604</v>
       </c>
       <c r="W92">
-        <v>0.2232707285579848</v>
+        <v>0.2234084128595454</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2656758151402711</v>
+        <v>0.2627563006881801</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.282157042784673</v>
+        <v>0.284057042784673</v>
       </c>
       <c r="C93">
-        <v>-21.57393723668044</v>
+        <v>-22.1887100390293</v>
       </c>
       <c r="D93">
-        <v>13.42676276331957</v>
+        <v>13.31968996097071</v>
       </c>
       <c r="E93">
-        <v>39.6307</v>
+        <v>40.1384</v>
       </c>
       <c r="F93">
-        <v>46.2007</v>
+        <v>46.7084</v>
       </c>
       <c r="G93">
         <v>11.2</v>
@@ -9047,37 +9047,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M93">
-        <v>10.89412506</v>
+        <v>11.01384072</v>
       </c>
       <c r="N93">
-        <v>-8.031625060000003</v>
+        <v>-8.151340720000002</v>
       </c>
       <c r="O93">
-        <v>-1.606325012000001</v>
+        <v>-1.630268144</v>
       </c>
       <c r="P93">
-        <v>-6.425300048000002</v>
+        <v>-6.521072576000002</v>
       </c>
       <c r="Q93">
-        <v>-5.275300048000002</v>
+        <v>-5.371072576000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8761709675831849</v>
+        <v>0.9799673385310833</v>
       </c>
       <c r="T93">
-        <v>9.092902444104997</v>
+        <v>10.22951524961812</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05255126013763604</v>
+        <v>0.05198005078831391</v>
       </c>
       <c r="W93">
-        <v>0.2234084128595454</v>
+        <v>0.2235431040241156</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2627563006881801</v>
+        <v>0.2599002539415695</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.284057042784673</v>
+        <v>0.285957042784673</v>
       </c>
       <c r="C94">
-        <v>-22.1887100390293</v>
+        <v>-22.80178863060588</v>
       </c>
       <c r="D94">
-        <v>13.31968996097071</v>
+        <v>13.21431136939413</v>
       </c>
       <c r="E94">
-        <v>40.1384</v>
+        <v>40.6461</v>
       </c>
       <c r="F94">
-        <v>46.7084</v>
+        <v>47.2161</v>
       </c>
       <c r="G94">
         <v>11.2</v>
@@ -9129,37 +9129,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M94">
-        <v>11.01384072</v>
+        <v>11.13355638</v>
       </c>
       <c r="N94">
-        <v>-8.151340720000002</v>
+        <v>-8.271056380000003</v>
       </c>
       <c r="O94">
-        <v>-1.630268144</v>
+        <v>-1.654211276000001</v>
       </c>
       <c r="P94">
-        <v>-6.521072576000002</v>
+        <v>-6.616845104000002</v>
       </c>
       <c r="Q94">
-        <v>-5.371072576000001</v>
+        <v>-5.466845104000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9799673385310833</v>
+        <v>1.113419815464096</v>
       </c>
       <c r="T94">
-        <v>10.22951524961812</v>
+        <v>11.69087457099214</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05198005078831391</v>
+        <v>0.05142112551102021</v>
       </c>
       <c r="W94">
-        <v>0.2235431040241156</v>
+        <v>0.2236748986045015</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2599002539415695</v>
+        <v>0.257105627555101</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.285957042784673</v>
+        <v>0.2878570427846729</v>
       </c>
       <c r="C95">
-        <v>-22.80178863060588</v>
+        <v>-23.4132129069707</v>
       </c>
       <c r="D95">
-        <v>13.21431136939413</v>
+        <v>13.11058709302931</v>
       </c>
       <c r="E95">
-        <v>40.6461</v>
+        <v>41.1538</v>
       </c>
       <c r="F95">
-        <v>47.2161</v>
+        <v>47.7238</v>
       </c>
       <c r="G95">
         <v>11.2</v>
@@ -9211,37 +9211,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M95">
-        <v>11.13355638</v>
+        <v>11.25327204</v>
       </c>
       <c r="N95">
-        <v>-8.271056380000003</v>
+        <v>-8.390772040000002</v>
       </c>
       <c r="O95">
-        <v>-1.654211276000001</v>
+        <v>-1.678154408</v>
       </c>
       <c r="P95">
-        <v>-6.616845104000002</v>
+        <v>-6.712617632000001</v>
       </c>
       <c r="Q95">
-        <v>-5.466845104000003</v>
+        <v>-5.562617632000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.113419815464096</v>
+        <v>1.291356451374778</v>
       </c>
       <c r="T95">
-        <v>11.69087457099214</v>
+        <v>13.6393536661575</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05142112551102021</v>
+        <v>0.05087409226090298</v>
       </c>
       <c r="W95">
-        <v>0.2236748986045015</v>
+        <v>0.2238038890448791</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.257105627555101</v>
+        <v>0.2543704613045148</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2878570427846729</v>
+        <v>0.289757042784673</v>
       </c>
       <c r="C96">
-        <v>-23.4132129069707</v>
+        <v>-24.02302152081688</v>
       </c>
       <c r="D96">
-        <v>13.11058709302931</v>
+        <v>13.00847847918313</v>
       </c>
       <c r="E96">
-        <v>41.1538</v>
+        <v>41.6615</v>
       </c>
       <c r="F96">
-        <v>47.7238</v>
+        <v>48.2315</v>
       </c>
       <c r="G96">
         <v>11.2</v>
@@ -9293,37 +9293,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M96">
-        <v>11.25327204</v>
+        <v>11.3729877</v>
       </c>
       <c r="N96">
-        <v>-8.390772040000002</v>
+        <v>-8.510487700000002</v>
       </c>
       <c r="O96">
-        <v>-1.678154408</v>
+        <v>-1.70209754</v>
       </c>
       <c r="P96">
-        <v>-6.712617632000001</v>
+        <v>-6.808390160000002</v>
       </c>
       <c r="Q96">
-        <v>-5.562617632000002</v>
+        <v>-5.658390160000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.291356451374778</v>
+        <v>1.540467741649735</v>
       </c>
       <c r="T96">
-        <v>13.6393536661575</v>
+        <v>16.36722439938901</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05087409226090298</v>
+        <v>0.05033857550026188</v>
       </c>
       <c r="W96">
-        <v>0.2238038890448791</v>
+        <v>0.2239301638970383</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2543704613045148</v>
+        <v>0.2516928775013094</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.289757042784673</v>
+        <v>0.291657042784673</v>
       </c>
       <c r="C97">
-        <v>-24.02302152081688</v>
+        <v>-24.63125192999492</v>
       </c>
       <c r="D97">
-        <v>13.00847847918313</v>
+        <v>12.90794807000508</v>
       </c>
       <c r="E97">
-        <v>41.6615</v>
+        <v>42.1692</v>
       </c>
       <c r="F97">
-        <v>48.2315</v>
+        <v>48.7392</v>
       </c>
       <c r="G97">
         <v>11.2</v>
@@ -9375,37 +9375,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M97">
-        <v>11.3729877</v>
+        <v>11.49270336</v>
       </c>
       <c r="N97">
-        <v>-8.510487700000002</v>
+        <v>-8.630203360000003</v>
       </c>
       <c r="O97">
-        <v>-1.70209754</v>
+        <v>-1.726040672000001</v>
       </c>
       <c r="P97">
-        <v>-6.808390160000002</v>
+        <v>-6.904162688000002</v>
       </c>
       <c r="Q97">
-        <v>-5.658390160000002</v>
+        <v>-5.754162688000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.540467741649735</v>
+        <v>1.914134677062169</v>
       </c>
       <c r="T97">
-        <v>16.36722439938901</v>
+        <v>20.45903049923627</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05033857550026188</v>
+        <v>0.04981421533880083</v>
       </c>
       <c r="W97">
-        <v>0.2239301638970383</v>
+        <v>0.2240538080231108</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2516928775013094</v>
+        <v>0.2490710766940041</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.291657042784673</v>
+        <v>0.293557042784673</v>
       </c>
       <c r="C98">
-        <v>-24.63125192999492</v>
+        <v>-25.23794044332782</v>
       </c>
       <c r="D98">
-        <v>12.90794807000508</v>
+        <v>12.80895955667219</v>
       </c>
       <c r="E98">
-        <v>42.1692</v>
+        <v>42.6769</v>
       </c>
       <c r="F98">
-        <v>48.7392</v>
+        <v>49.2469</v>
       </c>
       <c r="G98">
         <v>11.2</v>
@@ -9457,37 +9457,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M98">
-        <v>11.49270336</v>
+        <v>11.61241902</v>
       </c>
       <c r="N98">
-        <v>-8.630203360000003</v>
+        <v>-8.749919020000002</v>
       </c>
       <c r="O98">
-        <v>-1.726040672000001</v>
+        <v>-1.749983804</v>
       </c>
       <c r="P98">
-        <v>-6.904162688000002</v>
+        <v>-6.999935216000002</v>
       </c>
       <c r="Q98">
-        <v>-5.754162688000003</v>
+        <v>-5.849935216000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.914134677062164</v>
+        <v>2.536912902749552</v>
       </c>
       <c r="T98">
-        <v>20.45903049923622</v>
+        <v>27.27870733231496</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04981421533880083</v>
+        <v>0.04930066672706062</v>
       </c>
       <c r="W98">
-        <v>0.2240538080231108</v>
+        <v>0.2241749027857591</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2490710766940041</v>
+        <v>0.2465033336353031</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.293557042784673</v>
+        <v>0.2954570427846729</v>
       </c>
       <c r="C99">
-        <v>-25.23794044332782</v>
+        <v>-25.84312226433403</v>
       </c>
       <c r="D99">
-        <v>12.80895955667219</v>
+        <v>12.71147773566597</v>
       </c>
       <c r="E99">
-        <v>42.6769</v>
+        <v>43.1846</v>
       </c>
       <c r="F99">
-        <v>49.2469</v>
+        <v>49.7546</v>
       </c>
       <c r="G99">
         <v>11.2</v>
@@ -9539,37 +9539,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M99">
-        <v>11.61241902</v>
+        <v>11.73213468</v>
       </c>
       <c r="N99">
-        <v>-8.749919020000002</v>
+        <v>-8.869634680000003</v>
       </c>
       <c r="O99">
-        <v>-1.749983804</v>
+        <v>-1.773926936000001</v>
       </c>
       <c r="P99">
-        <v>-6.999935216000002</v>
+        <v>-7.095707744000002</v>
       </c>
       <c r="Q99">
-        <v>-5.849935216000002</v>
+        <v>-5.945707744000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.536912902749552</v>
+        <v>3.782469354124327</v>
       </c>
       <c r="T99">
-        <v>27.27870733231496</v>
+        <v>40.91806099847243</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04930066672706062</v>
+        <v>0.04879759869923347</v>
       </c>
       <c r="W99">
-        <v>0.2241749027857591</v>
+        <v>0.2242935262267207</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2465033336353031</v>
+        <v>0.2439879934961673</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2954570427846729</v>
+        <v>0.297357042784673</v>
       </c>
       <c r="C100">
-        <v>-25.84312226433403</v>
+        <v>-26.44683153296914</v>
       </c>
       <c r="D100">
-        <v>12.71147773566597</v>
+        <v>12.61546846703087</v>
       </c>
       <c r="E100">
-        <v>43.1846</v>
+        <v>43.6923</v>
       </c>
       <c r="F100">
-        <v>49.7546</v>
+        <v>50.2623</v>
       </c>
       <c r="G100">
         <v>11.2</v>
@@ -9621,37 +9621,37 @@
         <v>2.862499999999999</v>
       </c>
       <c r="M100">
-        <v>11.73213468</v>
+        <v>11.85185034</v>
       </c>
       <c r="N100">
-        <v>-8.869634680000003</v>
+        <v>-8.989350340000003</v>
       </c>
       <c r="O100">
-        <v>-1.773926936000001</v>
+        <v>-1.797870068000001</v>
       </c>
       <c r="P100">
-        <v>-7.095707744000002</v>
+        <v>-7.191480272000002</v>
       </c>
       <c r="Q100">
-        <v>-5.945707744000002</v>
+        <v>-6.041480272000003</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.782469354124327</v>
+        <v>7.519138708248655</v>
       </c>
       <c r="T100">
-        <v>40.91806099847243</v>
+        <v>81.83612199694487</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04879759869923347</v>
+        <v>0.04830469366186747</v>
       </c>
       <c r="W100">
-        <v>0.2242935262267207</v>
+        <v>0.2244097532345317</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2439879934961673</v>
+        <v>0.2415234683093372</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.297357042784673</v>
-      </c>
-      <c r="C101">
-        <v>-26.44683153296914</v>
-      </c>
-      <c r="D101">
-        <v>12.61546846703087</v>
-      </c>
-      <c r="E101">
-        <v>43.6923</v>
-      </c>
-      <c r="F101">
-        <v>50.2623</v>
-      </c>
-      <c r="G101">
-        <v>11.2</v>
-      </c>
-      <c r="H101">
-        <v>44.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.012499999999999</v>
-      </c>
-      <c r="K101">
-        <v>1.15</v>
-      </c>
-      <c r="L101">
-        <v>2.862499999999999</v>
-      </c>
-      <c r="M101">
-        <v>11.85185034</v>
-      </c>
-      <c r="N101">
-        <v>-8.989350340000003</v>
-      </c>
-      <c r="O101">
-        <v>-1.797870068000001</v>
-      </c>
-      <c r="P101">
-        <v>-7.191480272000002</v>
-      </c>
-      <c r="Q101">
-        <v>-6.041480272000003</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.519138708248655</v>
-      </c>
-      <c r="T101">
-        <v>81.83612199694487</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04830469366186747</v>
-      </c>
-      <c r="W101">
-        <v>0.2244097532345317</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2415234683093372</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
